--- a/Code/TCS_scripts_EN/TCS_scripts_EN_1/SI_Table_4.xlsx
+++ b/Code/TCS_scripts_EN/TCS_scripts_EN_1/SI_Table_4.xlsx
@@ -25,6 +25,7 @@
     <sheet name="15_TestSet_BackCalc" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="16_Train_RealConc" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="17_LoB_LoD_LoQ_Dist" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19_R1_Model" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,12 +918,12 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Exact_low</t>
+          <t>BetaQ_low</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>Exact_up</t>
+          <t>BetaQ_up</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
@@ -950,28 +951,28 @@
         <v>0.0251776210342589</v>
       </c>
       <c r="E3" t="n">
-        <v>100481.818509403</v>
+        <v>100481.812680611</v>
       </c>
       <c r="F3" t="n">
-        <v>4.18325758317425</v>
+        <v>4.183258762961561</v>
       </c>
       <c r="G3" t="n">
-        <v>92243.27984395438</v>
+        <v>92243.27216958524</v>
       </c>
       <c r="H3" t="n">
-        <v>108720.3571748517</v>
+        <v>108720.3531916368</v>
       </c>
       <c r="I3" t="n">
-        <v>92384.67187617833</v>
+        <v>92384.66423348364</v>
       </c>
       <c r="J3" t="n">
-        <v>109017.1503925709</v>
+        <v>109017.1464758427</v>
       </c>
       <c r="K3" t="n">
-        <v>92434.47976432448</v>
+        <v>92434.47213278736</v>
       </c>
       <c r="L3" t="n">
-        <v>108913.8033511197</v>
+        <v>108913.7994112412</v>
       </c>
     </row>
     <row r="4">
@@ -988,28 +989,28 @@
         <v>0.0264440667588355</v>
       </c>
       <c r="E4" t="n">
-        <v>106479.0505185144</v>
+        <v>106479.0460332074</v>
       </c>
       <c r="F4" t="n">
-        <v>4.105008531016773</v>
+        <v>4.105009623529461</v>
       </c>
       <c r="G4" t="n">
-        <v>97912.09869039716</v>
+        <v>97912.09228594272</v>
       </c>
       <c r="H4" t="n">
-        <v>115046.0023466316</v>
+        <v>115045.9997804721</v>
       </c>
       <c r="I4" t="n">
-        <v>98057.4678217905</v>
+        <v>98057.4614499013</v>
       </c>
       <c r="J4" t="n">
-        <v>115351.316952475</v>
+        <v>115351.3144547118</v>
       </c>
       <c r="K4" t="n">
-        <v>98108.8307699452</v>
+        <v>98108.824409557</v>
       </c>
       <c r="L4" t="n">
-        <v>115245.0212099571</v>
+        <v>115245.0186883846</v>
       </c>
     </row>
     <row r="5">
@@ -1026,28 +1027,28 @@
         <v>0.06340095324037209</v>
       </c>
       <c r="E5" t="n">
-        <v>285012.0341743743</v>
+        <v>285012.0696835865</v>
       </c>
       <c r="F5" t="n">
-        <v>2.548929821529851</v>
+        <v>2.548930074967541</v>
       </c>
       <c r="G5" t="n">
-        <v>270773.3726192513</v>
+        <v>270773.4049387536</v>
       </c>
       <c r="H5" t="n">
-        <v>299250.6957294973</v>
+        <v>299250.7344284194</v>
       </c>
       <c r="I5" t="n">
-        <v>270934.1228564534</v>
+        <v>270934.1552119656</v>
       </c>
       <c r="J5" t="n">
-        <v>299594.3004799662</v>
+        <v>299594.3392558619</v>
       </c>
       <c r="K5" t="n">
-        <v>270996.21508449</v>
+        <v>270996.247453903</v>
       </c>
       <c r="L5" t="n">
-        <v>299475.3015917896</v>
+        <v>299475.340341032</v>
       </c>
     </row>
     <row r="6">
@@ -1064,28 +1065,28 @@
         <v>0.0663932799138736</v>
       </c>
       <c r="E6" t="n">
-        <v>299774.4514275725</v>
+        <v>299774.4902438247</v>
       </c>
       <c r="F6" t="n">
-        <v>2.242481665019226</v>
+        <v>2.242481877006997</v>
       </c>
       <c r="G6" t="n">
-        <v>286598.8148024726</v>
+        <v>286598.8506671512</v>
       </c>
       <c r="H6" t="n">
-        <v>312950.0880526723</v>
+        <v>312950.1298204982</v>
       </c>
       <c r="I6" t="n">
-        <v>286729.7397892913</v>
+        <v>286729.7756833004</v>
       </c>
       <c r="J6" t="n">
-        <v>313230.2830788062</v>
+        <v>313230.3249094015</v>
       </c>
       <c r="K6" t="n">
-        <v>286780.82975729</v>
+        <v>286780.8656627524</v>
       </c>
       <c r="L6" t="n">
-        <v>313133.3735670879</v>
+        <v>313133.4153759681</v>
       </c>
     </row>
     <row r="7">
@@ -1102,28 +1103,28 @@
         <v>0.1653142731432553</v>
       </c>
       <c r="E7" t="n">
-        <v>816459.0552894928</v>
+        <v>816459.209852158</v>
       </c>
       <c r="F7" t="n">
-        <v>1.651940427420586</v>
+        <v>1.651940484757783</v>
       </c>
       <c r="G7" t="n">
-        <v>790024.2033180069</v>
+        <v>790024.3519588016</v>
       </c>
       <c r="H7" t="n">
-        <v>842893.9072609787</v>
+        <v>842894.0677455143</v>
       </c>
       <c r="I7" t="n">
-        <v>790212.9603036817</v>
+        <v>790213.1089867601</v>
       </c>
       <c r="J7" t="n">
-        <v>843322.8654150667</v>
+        <v>843323.0259956963</v>
       </c>
       <c r="K7" t="n">
-        <v>790303.6258262515</v>
+        <v>790303.7745296462</v>
       </c>
       <c r="L7" t="n">
-        <v>843174.8508097521</v>
+        <v>843175.0113572176</v>
       </c>
     </row>
     <row r="8">
@@ -1140,28 +1141,28 @@
         <v>0.178809366687342</v>
       </c>
       <c r="E8" t="n">
-        <v>891655.1181729696</v>
+        <v>891655.2895808712</v>
       </c>
       <c r="F8" t="n">
-        <v>1.277653620091134</v>
+        <v>1.277653660697368</v>
       </c>
       <c r="G8" t="n">
-        <v>869326.6912343065</v>
+        <v>869326.8576402491</v>
       </c>
       <c r="H8" t="n">
-        <v>913983.5451116326</v>
+        <v>913983.7215214934</v>
       </c>
       <c r="I8" t="n">
-        <v>869448.9715595815</v>
+        <v>869449.1379929163</v>
       </c>
       <c r="J8" t="n">
-        <v>914263.9829402588</v>
+        <v>914264.1594129468</v>
       </c>
       <c r="K8" t="n">
-        <v>869509.7544740846</v>
+        <v>869509.920921043</v>
       </c>
       <c r="L8" t="n">
-        <v>914167.3837782212</v>
+        <v>914167.5602292718</v>
       </c>
     </row>
     <row r="9">
@@ -1178,28 +1179,28 @@
         <v>0.4187649250990445</v>
       </c>
       <c r="E9" t="n">
-        <v>2485996.181518326</v>
+        <v>2485996.710086585</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8844995562758617</v>
+        <v>0.8844995663584876</v>
       </c>
       <c r="G9" t="n">
-        <v>2442899.26806743</v>
+        <v>2442899.786981224</v>
       </c>
       <c r="H9" t="n">
-        <v>2529093.094969222</v>
+        <v>2529093.633191946</v>
       </c>
       <c r="I9" t="n">
-        <v>2443035.487907357</v>
+        <v>2443036.006851675</v>
       </c>
       <c r="J9" t="n">
-        <v>2529479.961799069</v>
+        <v>2529480.500108457</v>
       </c>
       <c r="K9" t="n">
-        <v>2443152.189628418</v>
+        <v>2443152.708598909</v>
       </c>
       <c r="L9" t="n">
-        <v>2529346.918054816</v>
+        <v>2529347.456334396</v>
       </c>
     </row>
     <row r="10">
@@ -1216,28 +1217,28 @@
         <v>0.4415554783702524</v>
       </c>
       <c r="E10" t="n">
-        <v>2670526.397183298</v>
+        <v>2670526.967089561</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8794259116544322</v>
+        <v>0.8794259209865211</v>
       </c>
       <c r="G10" t="n">
-        <v>2624496.052832992</v>
+        <v>2624496.612427651</v>
       </c>
       <c r="H10" t="n">
-        <v>2716556.741533603</v>
+        <v>2716557.321751471</v>
       </c>
       <c r="I10" t="n">
-        <v>2624637.463869126</v>
+        <v>2624638.023495463</v>
       </c>
       <c r="J10" t="n">
-        <v>2716969.27344334</v>
+        <v>2716969.853753623</v>
       </c>
       <c r="K10" t="n">
-        <v>2624765.729827848</v>
+        <v>2624766.289482933</v>
       </c>
       <c r="L10" t="n">
-        <v>2716827.402337191</v>
+        <v>2716827.982615726</v>
       </c>
     </row>
     <row r="11">
@@ -1254,28 +1255,28 @@
         <v>0.8068136477061797</v>
       </c>
       <c r="E11" t="n">
-        <v>7567496.995392488</v>
+        <v>7567498.662306041</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7064597251126273</v>
+        <v>0.7064597277581509</v>
       </c>
       <c r="G11" t="n">
-        <v>7462714.736622212</v>
+        <v>7462716.380062702</v>
       </c>
       <c r="H11" t="n">
-        <v>7672279.254162764</v>
+        <v>7672280.944549381</v>
       </c>
       <c r="I11" t="n">
-        <v>7462844.469636031</v>
+        <v>7462846.113105587</v>
       </c>
       <c r="J11" t="n">
-        <v>7673176.483908588</v>
+        <v>7673178.174496199</v>
       </c>
       <c r="K11" t="n">
-        <v>7463299.408301521</v>
+        <v>7463301.051873028</v>
       </c>
       <c r="L11" t="n">
-        <v>7672867.820267681</v>
+        <v>7672869.510786172</v>
       </c>
     </row>
     <row r="12">
@@ -1292,28 +1293,28 @@
         <v>0.8254946711528661</v>
       </c>
       <c r="E12" t="n">
-        <v>8036665.068720676</v>
+        <v>8036666.840736107</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7190792799620027</v>
+        <v>0.719079282497583</v>
       </c>
       <c r="G12" t="n">
-        <v>7923398.763168001</v>
+        <v>7923400.509809793</v>
       </c>
       <c r="H12" t="n">
-        <v>8149931.374273351</v>
+        <v>8149933.171662421</v>
       </c>
       <c r="I12" t="n">
-        <v>7923531.338867114</v>
+        <v>7923533.085538586</v>
       </c>
       <c r="J12" t="n">
-        <v>8150940.438767422</v>
+        <v>8150942.236382539</v>
       </c>
       <c r="K12" t="n">
-        <v>7924055.840899482</v>
+        <v>7924057.587688483</v>
       </c>
       <c r="L12" t="n">
-        <v>8150593.216705978</v>
+        <v>8150595.014243313</v>
       </c>
     </row>
     <row r="13">
@@ -1330,28 +1331,28 @@
         <v>0.988450348319482</v>
       </c>
       <c r="E13" t="n">
-        <v>20563037.43359813</v>
+        <v>20563042.01174061</v>
       </c>
       <c r="F13" t="n">
-        <v>1.368871317474302</v>
+        <v>1.368871319360774</v>
       </c>
       <c r="G13" t="n">
-        <v>20011343.78928173</v>
+        <v>20011348.24383517</v>
       </c>
       <c r="H13" t="n">
-        <v>21114731.07791452</v>
+        <v>21114735.77964605</v>
       </c>
       <c r="I13" t="n">
-        <v>20011600.41537109</v>
+        <v>20011604.86998203</v>
       </c>
       <c r="J13" t="n">
-        <v>21132372.65780188</v>
+        <v>21132377.36348549</v>
       </c>
       <c r="K13" t="n">
-        <v>20022378.59064338</v>
+        <v>20022383.04766883</v>
       </c>
       <c r="L13" t="n">
-        <v>21126209.44958863</v>
+        <v>21126214.15389152</v>
       </c>
     </row>
     <row r="14">
@@ -1368,28 +1369,28 @@
         <v>0.9923915819004652</v>
       </c>
       <c r="E14" t="n">
-        <v>22488610.23406207</v>
+        <v>22488615.24356661</v>
       </c>
       <c r="F14" t="n">
-        <v>1.549330718756506</v>
+        <v>1.549330720708846</v>
       </c>
       <c r="G14" t="n">
-        <v>21805713.80738237</v>
+        <v>21805718.66390615</v>
       </c>
       <c r="H14" t="n">
-        <v>23171506.66074177</v>
+        <v>23171511.82322708</v>
       </c>
       <c r="I14" t="n">
-        <v>21806180.08252512</v>
+        <v>21806184.93915344</v>
       </c>
       <c r="J14" t="n">
-        <v>23198524.44183849</v>
+        <v>23198529.61037626</v>
       </c>
       <c r="K14" t="n">
-        <v>21822409.58602711</v>
+        <v>21822414.44629103</v>
       </c>
       <c r="L14" t="n">
-        <v>23189040.35251611</v>
+        <v>23189045.51892933</v>
       </c>
     </row>
     <row r="15">
@@ -1406,28 +1407,25 @@
         <v>0.9999982846612928</v>
       </c>
       <c r="E15" t="n">
-        <v>61227961.05960931</v>
+        <v>61227974.74748605</v>
       </c>
       <c r="F15" t="n">
-        <v>34.18501382055366</v>
+        <v>34.18501383691152</v>
       </c>
       <c r="G15" t="n">
-        <v>20204372.46899788</v>
+        <v>20204376.96617594</v>
       </c>
       <c r="H15" t="n">
-        <v>102251549.6502207</v>
+        <v>102251572.5287962</v>
       </c>
       <c r="I15" t="n">
-        <v>41128235.83223023</v>
+        <v>41128245.01733898</v>
       </c>
       <c r="J15" t="n">
-        <v>127469059.1934156</v>
+        <v>127469087.7487202</v>
       </c>
       <c r="K15" t="n">
-        <v>43736184.02071071</v>
-      </c>
-      <c r="L15" t="n">
-        <v/>
+        <v>43736193.79004369</v>
       </c>
     </row>
     <row r="16">
@@ -1444,28 +1442,25 @@
         <v>0.9999957919028676</v>
       </c>
       <c r="E16" t="n">
-        <v>57088025.67123029</v>
+        <v>57088038.43157438</v>
       </c>
       <c r="F16" t="n">
-        <v>23.22866452473772</v>
+        <v>23.22866453610032</v>
       </c>
       <c r="G16" t="n">
-        <v>31097362.76928233</v>
+        <v>31097369.70746676</v>
       </c>
       <c r="H16" t="n">
-        <v>83078688.57317826</v>
+        <v>83078707.15568201</v>
       </c>
       <c r="I16" t="n">
-        <v>41022053.99473796</v>
+        <v>41022063.15605655</v>
       </c>
       <c r="J16" t="n">
-        <v>127469059.1934156</v>
+        <v>127469087.7487202</v>
       </c>
       <c r="K16" t="n">
-        <v>43300722.42422916</v>
-      </c>
-      <c r="L16" t="n">
-        <v/>
+        <v>43300732.09601137</v>
       </c>
     </row>
   </sheetData>
@@ -1537,12 +1532,12 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>Exact_low</t>
+          <t>BetaQ_low</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Exact_up</t>
+          <t>BetaQ_up</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -1573,28 +1568,28 @@
         <v>0.2106910664406849</v>
       </c>
       <c r="F3" t="n">
-        <v>1074328.424730726</v>
+        <v>1074328.637060652</v>
       </c>
       <c r="G3" t="n">
-        <v>1.301187844375455</v>
+        <v>1.301187878697995</v>
       </c>
       <c r="H3" t="n">
-        <v>1046930.02768427</v>
+        <v>1046930.233876475</v>
       </c>
       <c r="I3" t="n">
-        <v>1101726.821777182</v>
+        <v>1101727.040244829</v>
       </c>
       <c r="J3" t="n">
-        <v>1047080.133690513</v>
+        <v>1047080.339916344</v>
       </c>
       <c r="K3" t="n">
-        <v>1102078.958485892</v>
+        <v>1102079.177032424</v>
       </c>
       <c r="L3" t="n">
-        <v>1047159.841621515</v>
+        <v>1047160.047865205</v>
       </c>
       <c r="M3" t="n">
-        <v>1101957.644056174</v>
+        <v>1101957.862575534</v>
       </c>
     </row>
     <row r="4">
@@ -1614,28 +1609,28 @@
         <v>0.2384781563280824</v>
       </c>
       <c r="F4" t="n">
-        <v>1239662.598689315</v>
+        <v>1239662.848056995</v>
       </c>
       <c r="G4" t="n">
-        <v>1.140729028491857</v>
+        <v>1.140729054568728</v>
       </c>
       <c r="H4" t="n">
-        <v>1211946.37339835</v>
+        <v>1211946.61655711</v>
       </c>
       <c r="I4" t="n">
-        <v>1267378.823980279</v>
+        <v>1267379.07955688</v>
       </c>
       <c r="J4" t="n">
-        <v>1212077.116665942</v>
+        <v>1212077.359853985</v>
       </c>
       <c r="K4" t="n">
-        <v>1267692.051564024</v>
+        <v>1267692.307210787</v>
       </c>
       <c r="L4" t="n">
-        <v>1212150.970193824</v>
+        <v>1212151.213398429</v>
       </c>
       <c r="M4" t="n">
-        <v>1267584.220576242</v>
+        <v>1267584.476198868</v>
       </c>
     </row>
     <row r="5">
@@ -1655,28 +1650,28 @@
         <v>0.9269920914207728</v>
       </c>
       <c r="F5" t="n">
-        <v>12056598.18358248</v>
+        <v>12056600.85613342</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8080286952268216</v>
+        <v>0.8080286971260557</v>
       </c>
       <c r="H5" t="n">
-        <v>11865656.977173</v>
+        <v>11865659.60694977</v>
       </c>
       <c r="I5" t="n">
-        <v>12247539.38999195</v>
+        <v>12247542.10531708</v>
       </c>
       <c r="J5" t="n">
-        <v>11865781.46561762</v>
+        <v>11865784.09542227</v>
       </c>
       <c r="K5" t="n">
-        <v>12249881.95121851</v>
+        <v>12249884.6670684</v>
       </c>
       <c r="L5" t="n">
-        <v>11867171.81500642</v>
+        <v>11867174.44512254</v>
       </c>
       <c r="M5" t="n">
-        <v>12249073.9444332</v>
+        <v>12249076.6601021</v>
       </c>
     </row>
     <row r="6">
@@ -1696,28 +1691,28 @@
         <v>0.9230378252624778</v>
       </c>
       <c r="F6" t="n">
-        <v>11813266.06762529</v>
+        <v>11813268.68566557</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8017180655797438</v>
+        <v>0.80171806750296</v>
       </c>
       <c r="H6" t="n">
-        <v>11627639.66574632</v>
+        <v>11627642.24220303</v>
       </c>
       <c r="I6" t="n">
-        <v>11998892.46950426</v>
+        <v>11998895.12912811</v>
       </c>
       <c r="J6" t="n">
-        <v>11627765.38552105</v>
+        <v>11627767.96200592</v>
       </c>
       <c r="K6" t="n">
-        <v>12001123.46618971</v>
+        <v>12001126.12631335</v>
       </c>
       <c r="L6" t="n">
-        <v>11629083.0647094</v>
+        <v>11629085.64148945</v>
       </c>
       <c r="M6" t="n">
-        <v>12000354.07371585</v>
+        <v>12000356.73366715</v>
       </c>
     </row>
     <row r="7">
@@ -1737,28 +1732,28 @@
         <v>0.0565362597315041</v>
       </c>
       <c r="F7" t="n">
-        <v>251323.0262357081</v>
+        <v>251323.0541979916</v>
       </c>
       <c r="G7" t="n">
-        <v>3.103705516841797</v>
+        <v>3.103705866806913</v>
       </c>
       <c r="H7" t="n">
-        <v>236034.6669725314</v>
+        <v>236034.6915099544</v>
       </c>
       <c r="I7" t="n">
-        <v>266611.3854988847</v>
+        <v>266611.4168860289</v>
       </c>
       <c r="J7" t="n">
-        <v>236244.2742228669</v>
+        <v>236244.2988072453</v>
       </c>
       <c r="K7" t="n">
-        <v>267058.1069330024</v>
+        <v>267058.1384202202</v>
       </c>
       <c r="L7" t="n">
-        <v>236323.5520321483</v>
+        <v>236323.5766342846</v>
       </c>
       <c r="M7" t="n">
-        <v>266903.0333418208</v>
+        <v>266903.0647943062</v>
       </c>
     </row>
     <row r="8">
@@ -1778,28 +1773,28 @@
         <v>0.0567395967084787</v>
       </c>
       <c r="F8" t="n">
-        <v>252317.390369096</v>
+        <v>252317.4185541343</v>
       </c>
       <c r="G8" t="n">
-        <v>2.851687419760262</v>
+        <v>2.851687740041331</v>
       </c>
       <c r="H8" t="n">
-        <v>238214.8550843682</v>
+        <v>238214.8801101912</v>
       </c>
       <c r="I8" t="n">
-        <v>266419.9256538239</v>
+        <v>266419.9569980773</v>
       </c>
       <c r="J8" t="n">
-        <v>238392.4290560439</v>
+        <v>238392.454121647</v>
       </c>
       <c r="K8" t="n">
-        <v>266798.2699697067</v>
+        <v>266798.3013987168</v>
       </c>
       <c r="L8" t="n">
-        <v>238459.8536872537</v>
+        <v>238459.8787679553</v>
       </c>
       <c r="M8" t="n">
-        <v>266667.0768048685</v>
+        <v>266667.1082044911</v>
       </c>
     </row>
     <row r="9">
@@ -1819,28 +1814,28 @@
         <v>0.2962727233488889</v>
       </c>
       <c r="F9" t="n">
-        <v>1603777.46800201</v>
+        <v>1603777.798937806</v>
       </c>
       <c r="G9" t="n">
-        <v>1.177153325303324</v>
+        <v>1.177153346103423</v>
       </c>
       <c r="H9" t="n">
-        <v>1566775.465136689</v>
+        <v>1566775.787783388</v>
       </c>
       <c r="I9" t="n">
-        <v>1640779.47086733</v>
+        <v>1640779.810092224</v>
       </c>
       <c r="J9" t="n">
-        <v>1566948.557781924</v>
+        <v>1566948.880467399</v>
       </c>
       <c r="K9" t="n">
-        <v>1641214.209835496</v>
+        <v>1641214.549157779</v>
       </c>
       <c r="L9" t="n">
-        <v>1567059.313851941</v>
+        <v>1567059.636562233</v>
       </c>
       <c r="M9" t="n">
-        <v>1641064.512088421</v>
+        <v>1641064.851377168</v>
       </c>
     </row>
     <row r="10">
@@ -1860,28 +1855,28 @@
         <v>0.3092185375698673</v>
       </c>
       <c r="F10" t="n">
-        <v>1689433.529282091</v>
+        <v>1689433.879406347</v>
       </c>
       <c r="G10" t="n">
-        <v>1.093340790597703</v>
+        <v>1.093340808937348</v>
       </c>
       <c r="H10" t="n">
-        <v>1653230.513358105</v>
+        <v>1653230.85537225</v>
       </c>
       <c r="I10" t="n">
-        <v>1725636.545206078</v>
+        <v>1725636.903440444</v>
       </c>
       <c r="J10" t="n">
-        <v>1653386.204973219</v>
+        <v>1653386.547022242</v>
       </c>
       <c r="K10" t="n">
-        <v>1726032.127542986</v>
+        <v>1726032.485865977</v>
       </c>
       <c r="L10" t="n">
-        <v>1653488.915383088</v>
+        <v>1653489.25745511</v>
       </c>
       <c r="M10" t="n">
-        <v>1725895.965962439</v>
+        <v>1725896.324254926</v>
       </c>
     </row>
     <row r="11">
@@ -1901,28 +1896,28 @@
         <v>0.0976629553295993</v>
       </c>
       <c r="F11" t="n">
-        <v>456934.9840411769</v>
+        <v>456935.0580641446</v>
       </c>
       <c r="G11" t="n">
-        <v>2.203534754080295</v>
+        <v>2.20353489074048</v>
       </c>
       <c r="H11" t="n">
-        <v>437200.65316408</v>
+        <v>437200.7227662115</v>
       </c>
       <c r="I11" t="n">
-        <v>476669.3149182739</v>
+        <v>476669.3933620778</v>
       </c>
       <c r="J11" t="n">
-        <v>437393.6088153252</v>
+        <v>437393.6784606816</v>
       </c>
       <c r="K11" t="n">
-        <v>477089.7415225899</v>
+        <v>477089.8200605788</v>
       </c>
       <c r="L11" t="n">
-        <v>437473.7477209386</v>
+        <v>437473.8173842397</v>
       </c>
       <c r="M11" t="n">
-        <v>476944.3275328652</v>
+        <v>476944.4060382868</v>
       </c>
     </row>
     <row r="12">
@@ -1942,28 +1937,28 @@
         <v>0.1006462696609974</v>
       </c>
       <c r="F12" t="n">
-        <v>472212.6373360435</v>
+        <v>472212.7147814739</v>
       </c>
       <c r="G12" t="n">
-        <v>2.197061409047274</v>
+        <v>2.197061540897566</v>
       </c>
       <c r="H12" t="n">
-        <v>451878.3998071288</v>
+        <v>451878.4726973335</v>
       </c>
       <c r="I12" t="n">
-        <v>492546.8748649581</v>
+        <v>492546.9568656144</v>
       </c>
       <c r="J12" t="n">
-        <v>452076.5300163413</v>
+        <v>452076.6029509304</v>
       </c>
       <c r="K12" t="n">
-        <v>492979.3350880452</v>
+        <v>492979.4171855802</v>
       </c>
       <c r="L12" t="n">
-        <v>452159.3157946775</v>
+        <v>452159.3887478053</v>
       </c>
       <c r="M12" t="n">
-        <v>492829.7614680181</v>
+        <v>492829.8435320603</v>
       </c>
     </row>
     <row r="13">
@@ -1983,28 +1978,28 @@
         <v>0.1185311629915233</v>
       </c>
       <c r="F13" t="n">
-        <v>564878.078858159</v>
+        <v>564878.1770622731</v>
       </c>
       <c r="G13" t="n">
-        <v>1.93236030132046</v>
+        <v>1.932360398261993</v>
       </c>
       <c r="H13" t="n">
-        <v>543484.1316806178</v>
+        <v>543484.2250921126</v>
       </c>
       <c r="I13" t="n">
-        <v>586272.0260357002</v>
+        <v>586272.1290324337</v>
       </c>
       <c r="J13" t="n">
-        <v>543666.4918004046</v>
+        <v>543666.5852527518</v>
       </c>
       <c r="K13" t="n">
-        <v>586674.2773607485</v>
+        <v>586674.3804475915</v>
       </c>
       <c r="L13" t="n">
-        <v>543745.7879997104</v>
+        <v>543745.8814698095</v>
       </c>
       <c r="M13" t="n">
-        <v>586535.3116496063</v>
+        <v>586535.4147053107</v>
       </c>
     </row>
     <row r="14">
@@ -2024,28 +2019,28 @@
         <v>0.1180170365692051</v>
       </c>
       <c r="F14" t="n">
-        <v>562188.1311586016</v>
+        <v>562188.2287601206</v>
       </c>
       <c r="G14" t="n">
-        <v>2.112410954944549</v>
+        <v>2.112411061425822</v>
       </c>
       <c r="H14" t="n">
-        <v>538912.1404750668</v>
+        <v>538912.2328623557</v>
       </c>
       <c r="I14" t="n">
-        <v>585464.1218421364</v>
+        <v>585464.2246578855</v>
       </c>
       <c r="J14" t="n">
-        <v>539129.1875679765</v>
+        <v>539129.2800038869</v>
       </c>
       <c r="K14" t="n">
-        <v>585942.8084328893</v>
+        <v>585942.9113558722</v>
       </c>
       <c r="L14" t="n">
-        <v>539223.2013436126</v>
+        <v>539223.2938005923</v>
       </c>
       <c r="M14" t="n">
-        <v>585777.3001862103</v>
+        <v>585777.4030721182</v>
       </c>
     </row>
     <row r="15">
@@ -2065,28 +2060,28 @@
         <v>0.2866570240223245</v>
       </c>
       <c r="F15" t="n">
-        <v>1541168.916957116</v>
+        <v>1541169.233867499</v>
       </c>
       <c r="G15" t="n">
-        <v>1.275726364948164</v>
+        <v>1.275726388405775</v>
       </c>
       <c r="H15" t="n">
-        <v>1502633.872584675</v>
+        <v>1502634.180862532</v>
       </c>
       <c r="I15" t="n">
-        <v>1579703.961329557</v>
+        <v>1579704.286872465</v>
       </c>
       <c r="J15" t="n">
-        <v>1502830.729697422</v>
+        <v>1502831.038019378</v>
       </c>
       <c r="K15" t="n">
-        <v>1580194.233230026</v>
+        <v>1580194.558882764</v>
       </c>
       <c r="L15" t="n">
-        <v>1502953.800412071</v>
+        <v>1502954.108761597</v>
       </c>
       <c r="M15" t="n">
-        <v>1580025.335282015</v>
+        <v>1580025.660896929</v>
       </c>
     </row>
     <row r="16">
@@ -2106,28 +2101,28 @@
         <v>0.2889233862063423</v>
       </c>
       <c r="F16" t="n">
-        <v>1555849.024507617</v>
+        <v>1555849.344706601</v>
       </c>
       <c r="G16" t="n">
-        <v>1.277118832420221</v>
+        <v>1.277118855681861</v>
       </c>
       <c r="H16" t="n">
-        <v>1516904.459980093</v>
+        <v>1516904.771454812</v>
       </c>
       <c r="I16" t="n">
-        <v>1594793.589035141</v>
+        <v>1594793.91795839</v>
       </c>
       <c r="J16" t="n">
-        <v>1517103.302207128</v>
+        <v>1517103.613726391</v>
       </c>
       <c r="K16" t="n">
-        <v>1595289.757265262</v>
+        <v>1595290.086299663</v>
       </c>
       <c r="L16" t="n">
-        <v>1517228.229736697</v>
+        <v>1517228.541283949</v>
       </c>
       <c r="M16" t="n">
-        <v>1595118.826410225</v>
+        <v>1595119.155406334</v>
       </c>
     </row>
     <row r="17">
@@ -2147,28 +2142,28 @@
         <v>0.0891853380125307</v>
       </c>
       <c r="F17" t="n">
-        <v>413794.9658588836</v>
+        <v>413795.0302177309</v>
       </c>
       <c r="G17" t="n">
-        <v>2.194927372371533</v>
+        <v>2.194927522689698</v>
       </c>
       <c r="H17" t="n">
-        <v>395993.5949858426</v>
+        <v>395993.6553568707</v>
       </c>
       <c r="I17" t="n">
-        <v>431596.3367319246</v>
+        <v>431596.4050785912</v>
       </c>
       <c r="J17" t="n">
-        <v>396167.1416124501</v>
+        <v>396167.2020223552</v>
       </c>
       <c r="K17" t="n">
-        <v>431972.5964066687</v>
+        <v>431972.664837624</v>
       </c>
       <c r="L17" t="n">
-        <v>396238.026208518</v>
+        <v>396238.0866343029</v>
       </c>
       <c r="M17" t="n">
-        <v>431842.4689311569</v>
+        <v>431842.5373329644</v>
       </c>
     </row>
     <row r="18">
@@ -2188,28 +2183,28 @@
         <v>0.0887975699638008</v>
       </c>
       <c r="F18" t="n">
-        <v>411831.3475412044</v>
+        <v>411831.4114601672</v>
       </c>
       <c r="G18" t="n">
-        <v>2.090347779016932</v>
+        <v>2.090347922855598</v>
       </c>
       <c r="H18" t="n">
-        <v>394958.5910315807</v>
+        <v>394958.6511707501</v>
       </c>
       <c r="I18" t="n">
-        <v>428704.104050828</v>
+        <v>428704.1717495843</v>
       </c>
       <c r="J18" t="n">
-        <v>395115.2065273528</v>
+        <v>395115.2667016062</v>
       </c>
       <c r="K18" t="n">
-        <v>429043.5362735239</v>
+        <v>429043.6040483184</v>
       </c>
       <c r="L18" t="n">
-        <v>395179.2265793375</v>
+        <v>395179.2867679293</v>
       </c>
       <c r="M18" t="n">
-        <v>428926.2012066381</v>
+        <v>428926.2689551427</v>
       </c>
     </row>
     <row r="19">
@@ -2229,28 +2224,28 @@
         <v>0.908920415707608</v>
       </c>
       <c r="F19" t="n">
-        <v>11036303.37989777</v>
+        <v>11036305.82388478</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8123999168652514</v>
+        <v>0.8123999189512917</v>
       </c>
       <c r="H19" t="n">
-        <v>10860575.12681775</v>
+        <v>10860577.53143855</v>
       </c>
       <c r="I19" t="n">
-        <v>11212031.63297778</v>
+        <v>11212034.11633101</v>
       </c>
       <c r="J19" t="n">
-        <v>10860715.12188057</v>
+        <v>10860717.52653274</v>
       </c>
       <c r="K19" t="n">
-        <v>11214087.61193975</v>
+        <v>11214090.09575356</v>
       </c>
       <c r="L19" t="n">
-        <v>10861906.53330672</v>
+        <v>10861908.93822576</v>
       </c>
       <c r="M19" t="n">
-        <v>11213378.76708523</v>
+        <v>11213381.25074024</v>
       </c>
     </row>
     <row r="20">
@@ -2270,28 +2265,28 @@
         <v>0.8969750377321517</v>
       </c>
       <c r="F20" t="n">
-        <v>10467776.70039624</v>
+        <v>10467779.01702331</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8464427544444582</v>
+        <v>0.8464427567359573</v>
       </c>
       <c r="H20" t="n">
-        <v>10294116.56613402</v>
+        <v>10294118.84385817</v>
       </c>
       <c r="I20" t="n">
-        <v>10641436.83465846</v>
+        <v>10641439.19018845</v>
       </c>
       <c r="J20" t="n">
-        <v>10294277.22989275</v>
+        <v>10294279.50765289</v>
       </c>
       <c r="K20" t="n">
-        <v>10643493.50323893</v>
+        <v>10643495.85922965</v>
       </c>
       <c r="L20" t="n">
-        <v>10295448.71464178</v>
+        <v>10295450.99266439</v>
       </c>
       <c r="M20" t="n">
-        <v>10642784.4053998</v>
+        <v>10642786.76123166</v>
       </c>
     </row>
     <row r="21">
@@ -2311,28 +2306,28 @@
         <v>0.2863305178695573</v>
       </c>
       <c r="F21" t="n">
-        <v>1539057.854383866</v>
+        <v>1539058.170821334</v>
       </c>
       <c r="G21" t="n">
-        <v>1.143103544420158</v>
+        <v>1.143103565467978</v>
       </c>
       <c r="H21" t="n">
-        <v>1504576.159231837</v>
+        <v>1504576.4679448</v>
       </c>
       <c r="I21" t="n">
-        <v>1573539.549535895</v>
+        <v>1573539.873697867</v>
       </c>
       <c r="J21" t="n">
-        <v>1504733.90422141</v>
+        <v>1504734.212969719</v>
       </c>
       <c r="K21" t="n">
-        <v>1573932.405571105</v>
+        <v>1573932.729821084</v>
       </c>
       <c r="L21" t="n">
-        <v>1504832.724519366</v>
+        <v>1504833.03328981</v>
       </c>
       <c r="M21" t="n">
-        <v>1573797.153474269</v>
+        <v>1573797.477693936</v>
       </c>
     </row>
     <row r="22">
@@ -2352,28 +2347,28 @@
         <v>0.2951619719410735</v>
       </c>
       <c r="F22" t="n">
-        <v>1596501.723006919</v>
+        <v>1596502.05231282</v>
       </c>
       <c r="G22" t="n">
-        <v>1.159164209593879</v>
+        <v>1.159164230169458</v>
       </c>
       <c r="H22" t="n">
-        <v>1560230.479417633</v>
+        <v>1560230.80059814</v>
       </c>
       <c r="I22" t="n">
-        <v>1632772.966596205</v>
+        <v>1632773.304027501</v>
       </c>
       <c r="J22" t="n">
-        <v>1560397.678245437</v>
+        <v>1560397.9994634</v>
       </c>
       <c r="K22" t="n">
-        <v>1633192.515558989</v>
+        <v>1633192.853084271</v>
       </c>
       <c r="L22" t="n">
-        <v>1560504.441492827</v>
+        <v>1560504.762734721</v>
       </c>
       <c r="M22" t="n">
-        <v>1633048.061028893</v>
+        <v>1633048.398521794</v>
       </c>
     </row>
     <row r="23">
@@ -2383,9 +2378,6 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2394,9 +2386,6 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2405,9 +2394,6 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2416,9 +2402,6 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2437,28 +2420,25 @@
         <v>0.9999999466406074</v>
       </c>
       <c r="F27" t="n">
-        <v>77237414.22356355</v>
+        <v>77237431.49740998</v>
       </c>
       <c r="G27" t="n">
-        <v>189.0885063480653</v>
+        <v>189.088506403939</v>
       </c>
       <c r="H27" t="n">
-        <v>-209009588.7024531</v>
+        <v>-209009635.5312153</v>
       </c>
       <c r="I27" t="n">
-        <v>363484417.1495802</v>
+        <v>363484498.5260353</v>
       </c>
       <c r="J27" t="n">
-        <v>39335907.82929993</v>
+        <v>39335916.61289488</v>
       </c>
       <c r="K27" t="n">
-        <v>127469059.1934156</v>
+        <v>127469087.7487202</v>
       </c>
       <c r="L27" t="n">
-        <v>42328520.98706261</v>
-      </c>
-      <c r="M27" t="n">
-        <v/>
+        <v>42328530.44105341</v>
       </c>
     </row>
     <row r="28">
@@ -2478,28 +2458,25 @@
         <v>0.9999999203000804</v>
       </c>
       <c r="F28" t="n">
-        <v>75386490.54393864</v>
+        <v>75386507.40622483</v>
       </c>
       <c r="G28" t="n">
-        <v>158.4576840616606</v>
+        <v>158.457684209219</v>
       </c>
       <c r="H28" t="n">
-        <v>-158742353.7466747</v>
+        <v>-158742389.4718438</v>
       </c>
       <c r="I28" t="n">
-        <v>309515334.834552</v>
+        <v>309515404.2842935</v>
       </c>
       <c r="J28" t="n">
-        <v>39338063.08197592</v>
+        <v>39338071.86605338</v>
       </c>
       <c r="K28" t="n">
-        <v>127469059.1934156</v>
+        <v>127469087.7487202</v>
       </c>
       <c r="L28" t="n">
-        <v>42323295.98208049</v>
-      </c>
-      <c r="M28" t="n">
-        <v/>
+        <v>42323305.43490319</v>
       </c>
     </row>
     <row r="29">
@@ -2519,28 +2496,28 @@
         <v>0.3412250216193241</v>
       </c>
       <c r="F29" t="n">
-        <v>1908293.257264303</v>
+        <v>1908293.656416976</v>
       </c>
       <c r="G29" t="n">
-        <v>1.14673114978914</v>
+        <v>1.14673116681829</v>
       </c>
       <c r="H29" t="n">
-        <v>1865403.378698032</v>
+        <v>1865403.768242621</v>
       </c>
       <c r="I29" t="n">
-        <v>1951183.135830574</v>
+        <v>1951183.544591332</v>
       </c>
       <c r="J29" t="n">
-        <v>1865592.094323302</v>
+        <v>1865592.483910159</v>
       </c>
       <c r="K29" t="n">
-        <v>1951676.896975781</v>
+        <v>1951677.30584715</v>
       </c>
       <c r="L29" t="n">
-        <v>1865725.762577453</v>
+        <v>1865726.152194261</v>
       </c>
       <c r="M29" t="n">
-        <v>1951506.890959141</v>
+        <v>1951507.299792426</v>
       </c>
     </row>
     <row r="30">
@@ -2560,28 +2537,28 @@
         <v>0.3438827957621401</v>
       </c>
       <c r="F30" t="n">
-        <v>1926942.70663212</v>
+        <v>1926943.109962597</v>
       </c>
       <c r="G30" t="n">
-        <v>1.102619383365052</v>
+        <v>1.102619399580663</v>
       </c>
       <c r="H30" t="n">
-        <v>1885299.658019229</v>
+        <v>1885300.052020933</v>
       </c>
       <c r="I30" t="n">
-        <v>1968585.755245012</v>
+        <v>1968586.167904263</v>
       </c>
       <c r="J30" t="n">
-        <v>1885475.398518685</v>
+        <v>1885475.792559759</v>
       </c>
       <c r="K30" t="n">
-        <v>1969046.802154681</v>
+        <v>1969047.214917215</v>
       </c>
       <c r="L30" t="n">
-        <v>1885600.761776738</v>
+        <v>1885601.155845892</v>
       </c>
       <c r="M30" t="n">
-        <v>1968888.093445471</v>
+        <v>1968888.50617244</v>
       </c>
     </row>
     <row r="31">
@@ -2601,28 +2578,25 @@
         <v>0.9999999893311496</v>
       </c>
       <c r="F31" t="n">
-        <v>84663471.53166728</v>
+        <v>84663490.49776962</v>
       </c>
       <c r="G31" t="n">
-        <v>406.4714000341325</v>
+        <v>406.4714025310199</v>
       </c>
       <c r="H31" t="n">
-        <v>-589824418.5497719</v>
+        <v>-589824554.8240552</v>
       </c>
       <c r="I31" t="n">
-        <v>759151361.6131064</v>
+        <v>759151535.8195944</v>
       </c>
       <c r="J31" t="n">
-        <v>38856136.30881161</v>
+        <v>38856144.98493005</v>
       </c>
       <c r="K31" t="n">
-        <v>127469059.1934156</v>
+        <v>127469087.7487202</v>
       </c>
       <c r="L31" t="n">
-        <v>41862625.29052399</v>
-      </c>
-      <c r="M31" t="n">
-        <v/>
+        <v>41862634.64014999</v>
       </c>
     </row>
     <row r="32">
@@ -2642,28 +2616,25 @@
         <v>0.9999999929925676</v>
       </c>
       <c r="F32" t="n">
-        <v>86602685.57863648</v>
+        <v>86602704.97915678</v>
       </c>
       <c r="G32" t="n">
-        <v>500.4745050221716</v>
+        <v>500.4745080965049</v>
       </c>
       <c r="H32" t="n">
-        <v>-762893453.9353683</v>
+        <v>-762893630.0551981</v>
       </c>
       <c r="I32" t="n">
-        <v>936098825.0926414</v>
+        <v>936099040.0135117</v>
       </c>
       <c r="J32" t="n">
-        <v>38667085.41359985</v>
+        <v>38667094.04736701</v>
       </c>
       <c r="K32" t="n">
-        <v>127469059.1934156</v>
+        <v>127469087.7487202</v>
       </c>
       <c r="L32" t="n">
-        <v>41674902.38942578</v>
-      </c>
-      <c r="M32" t="n">
-        <v/>
+        <v>41674911.69699524</v>
       </c>
     </row>
     <row r="33">
@@ -2683,28 +2654,28 @@
         <v>0.9684001270826436</v>
       </c>
       <c r="F33" t="n">
-        <v>15919805.93882503</v>
+        <v>15919809.47680226</v>
       </c>
       <c r="G33" t="n">
-        <v>1.131927370262306</v>
+        <v>1.131927372277225</v>
       </c>
       <c r="H33" t="n">
-        <v>15566619.17303414</v>
+        <v>15566622.63189135</v>
       </c>
       <c r="I33" t="n">
-        <v>16272992.70461591</v>
+        <v>16272996.32171318</v>
       </c>
       <c r="J33" t="n">
-        <v>15566795.36857899</v>
+        <v>15566798.82747566</v>
       </c>
       <c r="K33" t="n">
-        <v>16280435.3480769</v>
+        <v>16280438.96684144</v>
       </c>
       <c r="L33" t="n">
-        <v>15571361.065188</v>
+        <v>15571364.52510746</v>
       </c>
       <c r="M33" t="n">
-        <v>16277853.48542771</v>
+        <v>16277857.10361385</v>
       </c>
     </row>
     <row r="34">
@@ -2724,28 +2695,28 @@
         <v>0.9719385044096266</v>
       </c>
       <c r="F34" t="n">
-        <v>16467651.81882538</v>
+        <v>16467655.4795297</v>
       </c>
       <c r="G34" t="n">
-        <v>1.155960472479561</v>
+        <v>1.155960474468805</v>
       </c>
       <c r="H34" t="n">
-        <v>16094553.96500046</v>
+        <v>16094557.54212432</v>
       </c>
       <c r="I34" t="n">
-        <v>16840749.6726503</v>
+        <v>16840753.41693509</v>
       </c>
       <c r="J34" t="n">
-        <v>16094730.13809272</v>
+        <v>16094733.71525604</v>
       </c>
       <c r="K34" t="n">
-        <v>16849005.71540581</v>
+        <v>16849009.46154008</v>
       </c>
       <c r="L34" t="n">
-        <v>16099804.37540232</v>
+        <v>16099807.95370234</v>
       </c>
       <c r="M34" t="n">
-        <v>16846139.69353711</v>
+        <v>16846143.43902934</v>
       </c>
     </row>
     <row r="35">
@@ -2765,28 +2736,28 @@
         <v>0.9971122343547186</v>
       </c>
       <c r="F35" t="n">
-        <v>26957803.85048698</v>
+        <v>26957809.86116926</v>
       </c>
       <c r="G35" t="n">
-        <v>2.296513499389683</v>
+        <v>2.296513501803793</v>
       </c>
       <c r="H35" t="n">
-        <v>25744410.52233561</v>
+        <v>25744416.26119651</v>
       </c>
       <c r="I35" t="n">
-        <v>28171197.17863837</v>
+        <v>28171203.461142</v>
       </c>
       <c r="J35" t="n">
-        <v>25747659.0030477</v>
+        <v>25747664.74263632</v>
       </c>
       <c r="K35" t="n">
-        <v>28258307.01854528</v>
+        <v>28258313.32056308</v>
       </c>
       <c r="L35" t="n">
-        <v>25795652.53974539</v>
+        <v>25795658.29008546</v>
       </c>
       <c r="M35" t="n">
-        <v>28227118.98213384</v>
+        <v>28227125.27716511</v>
       </c>
     </row>
     <row r="36">
@@ -2806,28 +2777,28 @@
         <v>0.9982000642767084</v>
       </c>
       <c r="F36" t="n">
-        <v>29138637.82880498</v>
+        <v>29138644.32803239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.640515046143475</v>
+        <v>2.640515048711488</v>
       </c>
       <c r="H36" t="n">
-        <v>27630621.71188694</v>
+        <v>27630627.87329228</v>
       </c>
       <c r="I36" t="n">
-        <v>30646653.94572303</v>
+        <v>30646660.7827725</v>
       </c>
       <c r="J36" t="n">
-        <v>27637255.1426724</v>
+        <v>27637261.30556361</v>
       </c>
       <c r="K36" t="n">
-        <v>30783245.12573484</v>
+        <v>30783251.99338322</v>
       </c>
       <c r="L36" t="n">
-        <v>27708783.77814599</v>
+        <v>27708789.95706098</v>
       </c>
       <c r="M36" t="n">
-        <v>30733792.30327408</v>
+        <v>30733799.15984425</v>
       </c>
     </row>
     <row r="37">
@@ -2847,28 +2818,28 @@
         <v>0.9999538201831938</v>
       </c>
       <c r="F37" t="n">
-        <v>46036823.46932472</v>
+        <v>46036833.75403802</v>
       </c>
       <c r="G37" t="n">
-        <v>9.651134765423636</v>
+        <v>9.65113477135697</v>
       </c>
       <c r="H37" t="n">
-        <v>37328554.7742463</v>
+        <v>37328563.10816225</v>
       </c>
       <c r="I37" t="n">
-        <v>54745092.16440313</v>
+        <v>54745104.39991379</v>
       </c>
       <c r="J37" t="n">
-        <v>38349497.81327268</v>
+        <v>38349506.37589262</v>
       </c>
       <c r="K37" t="n">
-        <v>61944151.87152887</v>
+        <v>61944165.71996283</v>
       </c>
       <c r="L37" t="n">
-        <v>39392616.60221189</v>
+        <v>39392625.39851082</v>
       </c>
       <c r="M37" t="n">
-        <v>58564241.65763014</v>
+        <v>58564254.74882613</v>
       </c>
     </row>
     <row r="38">
@@ -2888,28 +2859,28 @@
         <v>0.999953403905856</v>
       </c>
       <c r="F38" t="n">
-        <v>45995424.65058806</v>
+        <v>45995434.92602864</v>
       </c>
       <c r="G38" t="n">
-        <v>9.481866193872117</v>
+        <v>9.481866199709099</v>
       </c>
       <c r="H38" t="n">
-        <v>37447581.46558152</v>
+        <v>37447589.82616027</v>
       </c>
       <c r="I38" t="n">
-        <v>54543267.83559459</v>
+        <v>54543280.025897</v>
       </c>
       <c r="J38" t="n">
-        <v>38423356.39923102</v>
+        <v>38423364.97839954</v>
       </c>
       <c r="K38" t="n">
-        <v>61411921.17789268</v>
+        <v>61411934.90706833</v>
       </c>
       <c r="L38" t="n">
-        <v>39445592.72366724</v>
+        <v>39445601.53183211</v>
       </c>
       <c r="M38" t="n">
-        <v>58200715.58980991</v>
+        <v>58200728.59939309</v>
       </c>
     </row>
     <row r="39">
@@ -2929,28 +2900,28 @@
         <v>0.9990444931181928</v>
       </c>
       <c r="F39" t="n">
-        <v>32060047.62747818</v>
+        <v>32060054.78115257</v>
       </c>
       <c r="G39" t="n">
-        <v>3.560933965314426</v>
+        <v>3.560933968461981</v>
       </c>
       <c r="H39" t="n">
-        <v>29822479.97854915</v>
+        <v>29822486.63096916</v>
       </c>
       <c r="I39" t="n">
-        <v>34297615.27640721</v>
+        <v>34297622.93133598</v>
       </c>
       <c r="J39" t="n">
-        <v>29845761.44422977</v>
+        <v>29845768.10186507</v>
       </c>
       <c r="K39" t="n">
-        <v>34611244.13074717</v>
+        <v>34611251.85593496</v>
       </c>
       <c r="L39" t="n">
-        <v>29989986.5026982</v>
+        <v>29989993.19264259</v>
       </c>
       <c r="M39" t="n">
-        <v>34494450.02964808</v>
+        <v>34494457.72867158</v>
       </c>
     </row>
     <row r="40">
@@ -2970,28 +2941,28 @@
         <v>0.9989296602098154</v>
       </c>
       <c r="F40" t="n">
-        <v>31536491.70888228</v>
+        <v>31536498.74527065</v>
       </c>
       <c r="G40" t="n">
-        <v>3.413862394641239</v>
+        <v>3.413862397708698</v>
       </c>
       <c r="H40" t="n">
-        <v>29426370.11873835</v>
+        <v>29426376.68242263</v>
       </c>
       <c r="I40" t="n">
-        <v>33646613.29902621</v>
+        <v>33646620.80811866</v>
       </c>
       <c r="J40" t="n">
-        <v>29445781.03125558</v>
+        <v>29445787.59928829</v>
       </c>
       <c r="K40" t="n">
-        <v>33923445.47625913</v>
+        <v>33923453.04736754</v>
       </c>
       <c r="L40" t="n">
-        <v>29576027.11319405</v>
+        <v>29576033.71040431</v>
       </c>
       <c r="M40" t="n">
-        <v>33820864.92691511</v>
+        <v>33820872.47504342</v>
       </c>
     </row>
     <row r="41">
@@ -3011,28 +2982,28 @@
         <v>0.8659939722722469</v>
       </c>
       <c r="F41" t="n">
-        <v>9254889.71277483</v>
+        <v>9254891.757693944</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8050371490616356</v>
+        <v>0.8050371515266594</v>
       </c>
       <c r="H41" t="n">
-        <v>9108862.007544149</v>
+        <v>9108864.019750493</v>
       </c>
       <c r="I41" t="n">
-        <v>9400917.418005511</v>
+        <v>9400919.495637393</v>
       </c>
       <c r="J41" t="n">
-        <v>9109019.698351121</v>
+        <v>9109021.710592795</v>
       </c>
       <c r="K41" t="n">
-        <v>9402463.713532871</v>
+        <v>9402465.791511146</v>
       </c>
       <c r="L41" t="n">
-        <v>9109866.054092214</v>
+        <v>9109868.066523504</v>
       </c>
       <c r="M41" t="n">
-        <v>9401931.045784136</v>
+        <v>9401933.123643089</v>
       </c>
     </row>
     <row r="42">
@@ -3052,28 +3023,28 @@
         <v>0.8969808401406735</v>
       </c>
       <c r="F42" t="n">
-        <v>10468036.52816641</v>
+        <v>10468038.84485169</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8823785399249428</v>
+        <v>0.8823785423136679</v>
       </c>
       <c r="H42" t="n">
-        <v>10286999.14739484</v>
+        <v>10287001.42352457</v>
       </c>
       <c r="I42" t="n">
-        <v>10649073.90893797</v>
+        <v>10649076.2661788</v>
       </c>
       <c r="J42" t="n">
-        <v>10287174.67528917</v>
+        <v>10287176.95145822</v>
       </c>
       <c r="K42" t="n">
-        <v>10651309.90035479</v>
+        <v>10651312.25809651</v>
       </c>
       <c r="L42" t="n">
-        <v>10288446.51249705</v>
+        <v>10288448.78895102</v>
       </c>
       <c r="M42" t="n">
-        <v>10650538.74628629</v>
+        <v>10650541.10385526</v>
       </c>
     </row>
     <row r="43">
@@ -3093,28 +3064,28 @@
         <v>0.9999895677777672</v>
       </c>
       <c r="F43" t="n">
-        <v>52899703.00037351</v>
+        <v>52899714.82246503</v>
       </c>
       <c r="G43" t="n">
-        <v>17.1043664768992</v>
+        <v>17.10436648595657</v>
       </c>
       <c r="H43" t="n">
-        <v>35165637.10388871</v>
+        <v>35165644.95335826</v>
       </c>
       <c r="I43" t="n">
-        <v>70633768.89685832</v>
+        <v>70633784.6915718</v>
       </c>
       <c r="J43" t="n">
-        <v>40047203.15363844</v>
+        <v>40047212.09657547</v>
       </c>
       <c r="K43" t="n">
-        <v>113933028.0457496</v>
+        <v>113933053.5687459</v>
       </c>
       <c r="L43" t="n">
-        <v>41937393.09190881</v>
+        <v>41937402.45828006</v>
       </c>
       <c r="M43" t="n">
-        <v>91598484.18181708</v>
+        <v>91598504.48642808</v>
       </c>
     </row>
     <row r="44">
@@ -3134,28 +3105,28 @@
         <v>0.9999914714452308</v>
       </c>
       <c r="F44" t="n">
-        <v>53829178.88250045</v>
+        <v>53829190.91288037</v>
       </c>
       <c r="G44" t="n">
-        <v>18.88702463408307</v>
+        <v>18.88702464416973</v>
       </c>
       <c r="H44" t="n">
-        <v>33902753.70127699</v>
+        <v>33902761.26762258</v>
       </c>
       <c r="I44" t="n">
-        <v>73755604.06372391</v>
+        <v>73755620.55813816</v>
       </c>
       <c r="J44" t="n">
-        <v>40019396.55865665</v>
+        <v>40019405.49536392</v>
       </c>
       <c r="K44" t="n">
-        <v>127469059.1934156</v>
+        <v>127469087.7487202</v>
       </c>
       <c r="L44" t="n">
-        <v>42037759.29215299</v>
+        <v>42037768.6810116</v>
       </c>
       <c r="M44" t="n">
-        <v>101477579.1334091</v>
+        <v>101477601.8661664</v>
       </c>
     </row>
     <row r="45">
@@ -3175,28 +3146,28 @@
         <v>0.9800109292641284</v>
       </c>
       <c r="F45" t="n">
-        <v>18032526.69136693</v>
+        <v>18032530.70263064</v>
       </c>
       <c r="G45" t="n">
-        <v>1.137848316240171</v>
+        <v>1.137848318028318</v>
       </c>
       <c r="H45" t="n">
-        <v>17630375.79050667</v>
+        <v>17630379.71168152</v>
       </c>
       <c r="I45" t="n">
-        <v>18434677.59222719</v>
+        <v>18434681.69357975</v>
       </c>
       <c r="J45" t="n">
-        <v>17630518.24490311</v>
+        <v>17630522.16610991</v>
       </c>
       <c r="K45" t="n">
-        <v>18444131.35587638</v>
+        <v>18444135.45934679</v>
       </c>
       <c r="L45" t="n">
-        <v>17636371.27075773</v>
+        <v>17636375.19327569</v>
       </c>
       <c r="M45" t="n">
-        <v>18440846.39452083</v>
+        <v>18440850.49725532</v>
       </c>
     </row>
     <row r="46">
@@ -3216,28 +3187,28 @@
         <v>0.9853753480289698</v>
       </c>
       <c r="F46" t="n">
-        <v>19474063.19623706</v>
+        <v>19474067.53043026</v>
       </c>
       <c r="G46" t="n">
-        <v>1.285161318419856</v>
+        <v>1.285161320290013</v>
       </c>
       <c r="H46" t="n">
-        <v>18983536.88038641</v>
+        <v>18983541.10469311</v>
       </c>
       <c r="I46" t="n">
-        <v>19964589.51208772</v>
+        <v>19964593.95616741</v>
       </c>
       <c r="J46" t="n">
-        <v>18983738.65574945</v>
+        <v>18983742.88010136</v>
       </c>
       <c r="K46" t="n">
-        <v>19978573.83133344</v>
+        <v>19978578.27854584</v>
       </c>
       <c r="L46" t="n">
-        <v>18992333.68339527</v>
+        <v>18992337.9096726</v>
       </c>
       <c r="M46" t="n">
-        <v>19973699.09113553</v>
+        <v>19973703.53725593</v>
       </c>
     </row>
     <row r="47">
@@ -3257,28 +3228,28 @@
         <v>0.9997838788642888</v>
       </c>
       <c r="F47" t="n">
-        <v>38917203.82925243</v>
+        <v>38917212.51905123</v>
       </c>
       <c r="G47" t="n">
-        <v>5.270177815722382</v>
+        <v>5.270177819561131</v>
       </c>
       <c r="H47" t="n">
-        <v>34897306.24546211</v>
+        <v>34897314.03473236</v>
       </c>
       <c r="I47" t="n">
-        <v>42937101.41304275</v>
+        <v>42937111.0033701</v>
       </c>
       <c r="J47" t="n">
-        <v>35029507.21341737</v>
+        <v>35029515.03230277</v>
       </c>
       <c r="K47" t="n">
-        <v>44068081.38084103</v>
+        <v>44068091.22453097</v>
       </c>
       <c r="L47" t="n">
-        <v>35405799.71915453</v>
+        <v>35405807.62233638</v>
       </c>
       <c r="M47" t="n">
-        <v>43616187.85959356</v>
+        <v>43616197.60204062</v>
       </c>
     </row>
     <row r="48">
@@ -3298,28 +3269,28 @@
         <v>0.9999122068639952</v>
       </c>
       <c r="F48" t="n">
-        <v>43073081.44734059</v>
+        <v>43073091.0681258</v>
       </c>
       <c r="G48" t="n">
-        <v>7.023743113933101</v>
+        <v>7.023743118551535</v>
       </c>
       <c r="H48" t="n">
-        <v>37143518.92589744</v>
+        <v>37143527.21835911</v>
       </c>
       <c r="I48" t="n">
-        <v>49002643.96878375</v>
+        <v>49002654.91789249</v>
       </c>
       <c r="J48" t="n">
-        <v>37528039.66640205</v>
+        <v>37528048.04500237</v>
       </c>
       <c r="K48" t="n">
-        <v>51793407.30322346</v>
+        <v>51793418.87749238</v>
       </c>
       <c r="L48" t="n">
-        <v>38184048.36727144</v>
+        <v>38184056.89282919</v>
       </c>
       <c r="M48" t="n">
-        <v>50593566.1918758</v>
+        <v>50593577.49738653</v>
       </c>
     </row>
     <row r="49">
@@ -3339,28 +3310,28 @@
         <v>0.999568855376163</v>
       </c>
       <c r="F49" t="n">
-        <v>35731268.78543372</v>
+        <v>35731276.76152606</v>
       </c>
       <c r="G49" t="n">
-        <v>4.023635434463077</v>
+        <v>4.023635437654228</v>
       </c>
       <c r="H49" t="n">
-        <v>32913436.42032958</v>
+        <v>32913443.76517805</v>
       </c>
       <c r="I49" t="n">
-        <v>38549101.15053786</v>
+        <v>38549109.75787407</v>
       </c>
       <c r="J49" t="n">
-        <v>32960272.35339377</v>
+        <v>32960279.70873406</v>
       </c>
       <c r="K49" t="n">
-        <v>39064066.44932342</v>
+        <v>39064075.17202185</v>
       </c>
       <c r="L49" t="n">
-        <v>33173607.51063153</v>
+        <v>33173614.91376265</v>
       </c>
       <c r="M49" t="n">
-        <v>38867877.75012479</v>
+        <v>38867886.42887138</v>
       </c>
     </row>
     <row r="50">
@@ -3380,28 +3351,28 @@
         <v>0.9995887676390042</v>
       </c>
       <c r="F50" t="n">
-        <v>35949407.38778657</v>
+        <v>35949415.41274475</v>
       </c>
       <c r="G50" t="n">
-        <v>4.882380154712283</v>
+        <v>4.882380158560042</v>
       </c>
       <c r="H50" t="n">
-        <v>32509304.60684961</v>
+        <v>32509311.86116521</v>
       </c>
       <c r="I50" t="n">
-        <v>39389510.16872354</v>
+        <v>39389518.96432428</v>
       </c>
       <c r="J50" t="n">
-        <v>32593871.21470021</v>
+        <v>32593878.48796015</v>
       </c>
       <c r="K50" t="n">
-        <v>40187731.65804107</v>
+        <v>40187740.63245623</v>
       </c>
       <c r="L50" t="n">
-        <v>32889051.22563137</v>
+        <v>32889058.56501702</v>
       </c>
       <c r="M50" t="n">
-        <v>39876036.9488266</v>
+        <v>39876045.85341978</v>
       </c>
     </row>
     <row r="51">
@@ -3421,28 +3392,28 @@
         <v>0.5176717745405706</v>
       </c>
       <c r="F51" t="n">
-        <v>3346508.69803108</v>
+        <v>3346509.419369233</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9166063887232092</v>
+        <v>0.916606396485098</v>
       </c>
       <c r="H51" t="n">
-        <v>3286388.150230906</v>
+        <v>3286388.858101002</v>
       </c>
       <c r="I51" t="n">
-        <v>3406629.245831254</v>
+        <v>3406629.980637465</v>
       </c>
       <c r="J51" t="n">
-        <v>3286565.074389378</v>
+        <v>3286565.78229912</v>
       </c>
       <c r="K51" t="n">
-        <v>3407200.469087396</v>
+        <v>3407201.204021559</v>
       </c>
       <c r="L51" t="n">
-        <v>3286761.274794383</v>
+        <v>3286761.982748065</v>
       </c>
       <c r="M51" t="n">
-        <v>3407003.95863456</v>
+        <v>3407004.693524712</v>
       </c>
     </row>
     <row r="52">
@@ -3462,28 +3433,28 @@
         <v>0.5247694755295773</v>
       </c>
       <c r="F52" t="n">
-        <v>3414899.503383836</v>
+        <v>3414900.240042729</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8004816198127408</v>
+        <v>0.8004816264555218</v>
       </c>
       <c r="H52" t="n">
-        <v>3361322.627884645</v>
+        <v>3361323.352541378</v>
       </c>
       <c r="I52" t="n">
-        <v>3468476.378883027</v>
+        <v>3468477.12754408</v>
       </c>
       <c r="J52" t="n">
-        <v>3361458.88950193</v>
+        <v>3361459.6141892</v>
       </c>
       <c r="K52" t="n">
-        <v>3468921.497009266</v>
+        <v>3468922.245770033</v>
       </c>
       <c r="L52" t="n">
-        <v>3361613.613613554</v>
+        <v>3361614.338335459</v>
       </c>
       <c r="M52" t="n">
-        <v>3468768.45888373</v>
+        <v>3468769.207610214</v>
       </c>
     </row>
     <row r="53">
@@ -3503,28 +3474,28 @@
         <v>0.6643772692472614</v>
       </c>
       <c r="F53" t="n">
-        <v>5019446.457792315</v>
+        <v>5019447.553897863</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8552729909603531</v>
+        <v>0.8552729957889998</v>
       </c>
       <c r="H53" t="n">
-        <v>4935305.263030465</v>
+        <v>4935306.340286911</v>
       </c>
       <c r="I53" t="n">
-        <v>5103587.652554165</v>
+        <v>5103588.767508816</v>
       </c>
       <c r="J53" t="n">
-        <v>4935490.012396077</v>
+        <v>4935491.08969391</v>
       </c>
       <c r="K53" t="n">
-        <v>5104373.643230956</v>
+        <v>5104374.758361683</v>
       </c>
       <c r="L53" t="n">
-        <v>4935818.091419477</v>
+        <v>4935819.168790805</v>
       </c>
       <c r="M53" t="n">
-        <v>5104103.218374465</v>
+        <v>5104104.333444629</v>
       </c>
     </row>
     <row r="54">
@@ -3544,28 +3515,28 @@
         <v>0.686187545130247</v>
       </c>
       <c r="F54" t="n">
-        <v>5329421.116772774</v>
+        <v>5329422.282318082</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8611066761688886</v>
+        <v>0.8611066807477067</v>
       </c>
       <c r="H54" t="n">
-        <v>5239474.447560436</v>
+        <v>5239475.592956114</v>
       </c>
       <c r="I54" t="n">
-        <v>5419367.785985111</v>
+        <v>5419368.97168005</v>
       </c>
       <c r="J54" t="n">
-        <v>5239664.926052</v>
+        <v>5239666.07149035</v>
       </c>
       <c r="K54" t="n">
-        <v>5420223.430978775</v>
+        <v>5420224.616865394</v>
       </c>
       <c r="L54" t="n">
-        <v>5240032.499126728</v>
+        <v>5240033.644647428</v>
       </c>
       <c r="M54" t="n">
-        <v>5419929.00324672</v>
+        <v>5419930.189067395</v>
       </c>
     </row>
     <row r="55">
@@ -3585,28 +3556,28 @@
         <v>0.3168410560066339</v>
       </c>
       <c r="F55" t="n">
-        <v>1740622.04503036</v>
+        <v>1740622.406621742</v>
       </c>
       <c r="G55" t="n">
-        <v>1.274057940582487</v>
+        <v>1.274057961324991</v>
       </c>
       <c r="H55" t="n">
-        <v>1697156.838303142</v>
+        <v>1697157.190157555</v>
       </c>
       <c r="I55" t="n">
-        <v>1784087.251757578</v>
+        <v>1784087.623085928</v>
       </c>
       <c r="J55" t="n">
-        <v>1697373.658715016</v>
+        <v>1697374.010617999</v>
       </c>
       <c r="K55" t="n">
-        <v>1784641.674131944</v>
+        <v>1784642.045584494</v>
       </c>
       <c r="L55" t="n">
-        <v>1697518.583859896</v>
+        <v>1697518.935795347</v>
       </c>
       <c r="M55" t="n">
-        <v>1784450.670416676</v>
+        <v>1784451.041826434</v>
       </c>
     </row>
     <row r="56">
@@ -3626,28 +3597,28 @@
         <v>0.3025717897803709</v>
       </c>
       <c r="F56" t="n">
-        <v>1645256.658884253</v>
+        <v>1645256.999112116</v>
       </c>
       <c r="G56" t="n">
-        <v>1.264066371548494</v>
+        <v>1.264066393321215</v>
       </c>
       <c r="H56" t="n">
-        <v>1604495.021047466</v>
+        <v>1604495.352144006</v>
       </c>
       <c r="I56" t="n">
-        <v>1686018.296721041</v>
+        <v>1686018.646080225</v>
       </c>
       <c r="J56" t="n">
-        <v>1604698.939882593</v>
+        <v>1604699.271024824</v>
       </c>
       <c r="K56" t="n">
-        <v>1686533.175413042</v>
+        <v>1686533.524887576</v>
       </c>
       <c r="L56" t="n">
-        <v>1604831.007501863</v>
+        <v>1604831.338673668</v>
       </c>
       <c r="M56" t="n">
-        <v>1686355.806799353</v>
+        <v>1686356.156234148</v>
       </c>
     </row>
     <row r="57">
@@ -3667,28 +3638,28 @@
         <v>0.2595353119189137</v>
       </c>
       <c r="F57" t="n">
-        <v>1369022.482546122</v>
+        <v>1369022.760892685</v>
       </c>
       <c r="G57" t="n">
-        <v>1.353203607822664</v>
+        <v>1.353203635833692</v>
       </c>
       <c r="H57" t="n">
-        <v>1332712.85296994</v>
+        <v>1332713.123182509</v>
       </c>
       <c r="I57" t="n">
-        <v>1405332.112122304</v>
+        <v>1405332.398602861</v>
       </c>
       <c r="J57" t="n">
-        <v>1332913.459834848</v>
+        <v>1332913.73009236</v>
       </c>
       <c r="K57" t="n">
-        <v>1405820.620282332</v>
+        <v>1405820.906872323</v>
       </c>
       <c r="L57" t="n">
-        <v>1333031.515441754</v>
+        <v>1333031.785725708</v>
       </c>
       <c r="M57" t="n">
-        <v>1405652.273257473</v>
+        <v>1405652.559809746</v>
       </c>
     </row>
     <row r="58">
@@ -3708,28 +3679,28 @@
         <v>0.2661103226484039</v>
       </c>
       <c r="F58" t="n">
-        <v>1410169.17765927</v>
+        <v>1410169.465223414</v>
       </c>
       <c r="G58" t="n">
-        <v>1.159206148109639</v>
+        <v>1.159206171404812</v>
       </c>
       <c r="H58" t="n">
-        <v>1378130.101495531</v>
+        <v>1378130.38188236</v>
       </c>
       <c r="I58" t="n">
-        <v>1442208.253823009</v>
+        <v>1442208.548564468</v>
       </c>
       <c r="J58" t="n">
-        <v>1378280.890588324</v>
+        <v>1378281.171008933</v>
       </c>
       <c r="K58" t="n">
-        <v>1442577.510469181</v>
+        <v>1442577.805293359</v>
       </c>
       <c r="L58" t="n">
-        <v>1378371.24824078</v>
+        <v>1378371.528681618</v>
       </c>
       <c r="M58" t="n">
-        <v>1442450.376158292</v>
+        <v>1442450.670953991</v>
       </c>
     </row>
     <row r="59">
@@ -3749,28 +3720,28 @@
         <v>0.9999585115158668</v>
       </c>
       <c r="F59" t="n">
-        <v>46531027.39827123</v>
+        <v>46531037.79370012</v>
       </c>
       <c r="G59" t="n">
-        <v>9.421980160751009</v>
+        <v>9.421980166491482</v>
       </c>
       <c r="H59" t="n">
-        <v>37938262.72192487</v>
+        <v>37938271.19242149</v>
       </c>
       <c r="I59" t="n">
-        <v>55123792.07461758</v>
+        <v>55123804.39497875</v>
       </c>
       <c r="J59" t="n">
-        <v>38926552.42250706</v>
+        <v>38926561.11439704</v>
       </c>
       <c r="K59" t="n">
-        <v>62083891.80037463</v>
+        <v>62083905.67996353</v>
       </c>
       <c r="L59" t="n">
-        <v>39954666.30841766</v>
+        <v>39954675.2306229</v>
       </c>
       <c r="M59" t="n">
-        <v>58826049.89402854</v>
+        <v>58826063.04364014</v>
       </c>
     </row>
     <row r="60">
@@ -3790,28 +3761,28 @@
         <v>0.9999539617978218</v>
       </c>
       <c r="F60" t="n">
-        <v>46050992.17446231</v>
+        <v>46051002.46235114</v>
       </c>
       <c r="G60" t="n">
-        <v>8.352892031328087</v>
+        <v>8.352892036464125</v>
       </c>
       <c r="H60" t="n">
-        <v>38511814.98600914</v>
+        <v>38511823.58499418</v>
       </c>
       <c r="I60" t="n">
-        <v>53590169.36291548</v>
+        <v>53590181.3397081</v>
       </c>
       <c r="J60" t="n">
-        <v>39226720.69218923</v>
+        <v>39226729.45132313</v>
       </c>
       <c r="K60" t="n">
-        <v>58604690.51449109</v>
+        <v>58604703.61466822</v>
       </c>
       <c r="L60" t="n">
-        <v>40113076.94439912</v>
+        <v>40113085.90209548</v>
       </c>
       <c r="M60" t="n">
-        <v>56327636.68900384</v>
+        <v>56327649.27910312</v>
       </c>
     </row>
     <row r="61">
@@ -3831,28 +3802,28 @@
         <v>0.9738706191312664</v>
       </c>
       <c r="F61" t="n">
-        <v>16796752.17659403</v>
+        <v>16796755.91102258</v>
       </c>
       <c r="G61" t="n">
-        <v>1.056022616428562</v>
+        <v>1.05602261821022</v>
       </c>
       <c r="H61" t="n">
-        <v>16449098.66137817</v>
+        <v>16449102.31792624</v>
       </c>
       <c r="I61" t="n">
-        <v>17144405.69180988</v>
+        <v>17144409.50411892</v>
       </c>
       <c r="J61" t="n">
-        <v>16449228.02252523</v>
+        <v>16449231.67910231</v>
       </c>
       <c r="K61" t="n">
-        <v>17151536.39909698</v>
+        <v>17151540.21300342</v>
       </c>
       <c r="L61" t="n">
-        <v>16453643.6983785</v>
+        <v>16453647.35594475</v>
       </c>
       <c r="M61" t="n">
-        <v>17149063.44247649</v>
+        <v>17149067.25582895</v>
       </c>
     </row>
     <row r="62">
@@ -3872,28 +3843,28 @@
         <v>0.978026424452201</v>
       </c>
       <c r="F62" t="n">
-        <v>17595859.19141616</v>
+        <v>17595863.10485872</v>
       </c>
       <c r="G62" t="n">
-        <v>1.041739197034266</v>
+        <v>1.041739198712008</v>
       </c>
       <c r="H62" t="n">
-        <v>17236591.98714286</v>
+        <v>17236595.82010326</v>
       </c>
       <c r="I62" t="n">
-        <v>17955126.39568947</v>
+        <v>17955130.38961418</v>
       </c>
       <c r="J62" t="n">
-        <v>17236703.36173777</v>
+        <v>17236707.19472312</v>
       </c>
       <c r="K62" t="n">
-        <v>17962683.39838592</v>
+        <v>17962687.39400351</v>
       </c>
       <c r="L62" t="n">
-        <v>17241403.37053128</v>
+        <v>17241407.2045695</v>
       </c>
       <c r="M62" t="n">
-        <v>17960061.61636324</v>
+        <v>17960065.61139353</v>
       </c>
     </row>
     <row r="63">
@@ -3913,28 +3884,28 @@
         <v>0.7308584339589387</v>
       </c>
       <c r="F63" t="n">
-        <v>6037823.485078179</v>
+        <v>6037824.80931804</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7161033877750151</v>
+        <v>0.7161033911360405</v>
       </c>
       <c r="H63" t="n">
-        <v>5953080.407572669</v>
+        <v>5953081.712828594</v>
       </c>
       <c r="I63" t="n">
-        <v>6122566.56258369</v>
+        <v>6122567.905807487</v>
       </c>
       <c r="J63" t="n">
-        <v>5953214.617267507</v>
+        <v>5953215.922553514</v>
       </c>
       <c r="K63" t="n">
-        <v>6123255.046649628</v>
+        <v>6123256.390027658</v>
       </c>
       <c r="L63" t="n">
-        <v>5953529.74845526</v>
+        <v>5953531.053811844</v>
       </c>
       <c r="M63" t="n">
-        <v>6123018.292574949</v>
+        <v>6123019.635899954</v>
       </c>
     </row>
     <row r="64">
@@ -3954,28 +3925,28 @@
         <v>0.7179658519502181</v>
       </c>
       <c r="F64" t="n">
-        <v>5821966.280527842</v>
+        <v>5821967.556411906</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7067799623245812</v>
+        <v>0.7067799657648391</v>
       </c>
       <c r="H64" t="n">
-        <v>5741316.719984909</v>
+        <v>5741317.977802056</v>
       </c>
       <c r="I64" t="n">
-        <v>5902615.841070776</v>
+        <v>5902617.135021756</v>
       </c>
       <c r="J64" t="n">
-        <v>5741446.764955205</v>
+        <v>5741448.022801485</v>
       </c>
       <c r="K64" t="n">
-        <v>5903256.942201698</v>
+        <v>5903258.236296277</v>
       </c>
       <c r="L64" t="n">
-        <v>5741735.268154823</v>
+        <v>5741736.526065711</v>
       </c>
       <c r="M64" t="n">
-        <v>5903036.507837393</v>
+        <v>5903037.801882599</v>
       </c>
     </row>
     <row r="65">
@@ -3995,28 +3966,28 @@
         <v>0.3880655224327178</v>
       </c>
       <c r="F65" t="n">
-        <v>2248552.226373024</v>
+        <v>2248552.701749674</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9314401485444576</v>
+        <v>0.9314401602833864</v>
       </c>
       <c r="H65" t="n">
-        <v>2207502.901010911</v>
+        <v>2207503.367191792</v>
       </c>
       <c r="I65" t="n">
-        <v>2289601.551735137</v>
+        <v>2289602.036307556</v>
       </c>
       <c r="J65" t="n">
-        <v>2207643.580154042</v>
+        <v>2207644.046366437</v>
       </c>
       <c r="K65" t="n">
-        <v>2289987.699229439</v>
+        <v>2289988.183888369</v>
       </c>
       <c r="L65" t="n">
-        <v>2207755.312432047</v>
+        <v>2207755.778669514</v>
       </c>
       <c r="M65" t="n">
-        <v>2289854.877434711</v>
+        <v>2289855.362063804</v>
       </c>
     </row>
     <row r="66">
@@ -4036,28 +4007,28 @@
         <v>0.3873361701360253</v>
       </c>
       <c r="F66" t="n">
-        <v>2243057.054948182</v>
+        <v>2243057.529093816</v>
       </c>
       <c r="G66" t="n">
-        <v>0.954137897810226</v>
+        <v>0.9541379098646732</v>
       </c>
       <c r="H66" t="n">
-        <v>2201110.185181619</v>
+        <v>2201110.649930418</v>
       </c>
       <c r="I66" t="n">
-        <v>2285003.924714745</v>
+        <v>2285004.408257214</v>
       </c>
       <c r="J66" t="n">
-        <v>2201257.5703347</v>
+        <v>2201258.035116516</v>
       </c>
       <c r="K66" t="n">
-        <v>2285408.125789054</v>
+        <v>2285408.609422071</v>
       </c>
       <c r="L66" t="n">
-        <v>2201374.359729296</v>
+        <v>2201374.824537255</v>
       </c>
       <c r="M66" t="n">
-        <v>2285269.078721761</v>
+        <v>2285269.562323624</v>
       </c>
     </row>
     <row r="67">
@@ -4077,28 +4048,28 @@
         <v>0.1518208154702773</v>
       </c>
       <c r="F67" t="n">
-        <v>742477.9531857216</v>
+        <v>742478.0911753221</v>
       </c>
       <c r="G67" t="n">
-        <v>1.890633710389976</v>
+        <v>1.890633782550608</v>
       </c>
       <c r="H67" t="n">
-        <v>714964.8833428465</v>
+        <v>714965.0151690368</v>
       </c>
       <c r="I67" t="n">
-        <v>769991.0230285968</v>
+        <v>769991.1671816073</v>
       </c>
       <c r="J67" t="n">
-        <v>715191.3624571402</v>
+        <v>715191.4943340657</v>
       </c>
       <c r="K67" t="n">
-        <v>770501.1859988492</v>
+        <v>770501.3302661454</v>
       </c>
       <c r="L67" t="n">
-        <v>715296.7653203808</v>
+        <v>715296.8972209224</v>
       </c>
       <c r="M67" t="n">
-        <v>770324.9599694379</v>
+        <v>770325.1041972548</v>
       </c>
     </row>
     <row r="68">
@@ -4118,28 +4089,28 @@
         <v>0.1492695571555508</v>
       </c>
       <c r="F68" t="n">
-        <v>728622.4604232189</v>
+        <v>728622.5953089464</v>
       </c>
       <c r="G68" t="n">
-        <v>1.439335037329728</v>
+        <v>1.439335093310107</v>
       </c>
       <c r="H68" t="n">
-        <v>708067.6941378717</v>
+        <v>708067.8244189711</v>
       </c>
       <c r="I68" t="n">
-        <v>749177.2267085661</v>
+        <v>749177.3661989218</v>
       </c>
       <c r="J68" t="n">
-        <v>708196.4406452315</v>
+        <v>708196.5709551724</v>
       </c>
       <c r="K68" t="n">
-        <v>749466.7050169579</v>
+        <v>749466.8445721617</v>
       </c>
       <c r="L68" t="n">
-        <v>708256.4995417272</v>
+        <v>708256.6298651214</v>
       </c>
       <c r="M68" t="n">
-        <v>749366.9203529768</v>
+        <v>749367.0598858335</v>
       </c>
     </row>
     <row r="69">
@@ -4159,28 +4130,28 @@
         <v>0.0585443041728947</v>
       </c>
       <c r="F69" t="n">
-        <v>261152.2265430845</v>
+        <v>261152.256707281</v>
       </c>
       <c r="G69" t="n">
-        <v>2.672165661300336</v>
+        <v>2.672165951265735</v>
       </c>
       <c r="H69" t="n">
-        <v>247474.77443614</v>
+        <v>247474.8015363473</v>
       </c>
       <c r="I69" t="n">
-        <v>274829.678650029</v>
+        <v>274829.7118782147</v>
       </c>
       <c r="J69" t="n">
-        <v>247636.2823321098</v>
+        <v>247636.3094684974</v>
       </c>
       <c r="K69" t="n">
-        <v>275174.038545721</v>
+        <v>275174.0718510505</v>
       </c>
       <c r="L69" t="n">
-        <v>247697.9749350476</v>
+        <v>247698.0020852541</v>
       </c>
       <c r="M69" t="n">
-        <v>275054.7205384756</v>
+        <v>275054.7538170824</v>
       </c>
     </row>
     <row r="70">
@@ -4200,28 +4171,28 @@
         <v>0.0595571691496807</v>
       </c>
       <c r="F70" t="n">
-        <v>266118.0684310353</v>
+        <v>266118.0997076678</v>
       </c>
       <c r="G70" t="n">
-        <v>2.74066758410962</v>
+        <v>2.740667875958833</v>
       </c>
       <c r="H70" t="n">
-        <v>251823.2442981918</v>
+        <v>251823.2723725331</v>
       </c>
       <c r="I70" t="n">
-        <v>280412.8925638788</v>
+        <v>280412.9270428026</v>
       </c>
       <c r="J70" t="n">
-        <v>251996.5033604136</v>
+        <v>251996.5314735686</v>
       </c>
       <c r="K70" t="n">
-        <v>280782.5535365188</v>
+        <v>280782.5880982535</v>
       </c>
       <c r="L70" t="n">
-        <v>252062.7508979492</v>
+        <v>252062.7790259468</v>
       </c>
       <c r="M70" t="n">
-        <v>280654.4285159057</v>
+        <v>280654.4630489398</v>
       </c>
     </row>
     <row r="71">
@@ -4241,28 +4212,28 @@
         <v>0.0222068730908465</v>
       </c>
       <c r="F71" t="n">
-        <v>86444.41124704164</v>
+        <v>86444.40227362431</v>
       </c>
       <c r="G71" t="n">
-        <v>4.726384047519583</v>
+        <v>4.726385596937972</v>
       </c>
       <c r="H71" t="n">
-        <v>78436.59646344263</v>
+        <v>78436.58569613435</v>
       </c>
       <c r="I71" t="n">
-        <v>94452.22603064064</v>
+        <v>94452.21885111426</v>
       </c>
       <c r="J71" t="n">
-        <v>78588.61843400575</v>
+        <v>78588.60770075323</v>
       </c>
       <c r="K71" t="n">
-        <v>94771.09660010586</v>
+        <v>94771.08949201203</v>
       </c>
       <c r="L71" t="n">
-        <v>78641.5833058087</v>
+        <v>78641.57258442094</v>
       </c>
       <c r="M71" t="n">
-        <v>94659.8721728883</v>
+        <v>94659.8650398782</v>
       </c>
     </row>
     <row r="72">
@@ -4282,28 +4253,28 @@
         <v>0.0208297875707025</v>
       </c>
       <c r="F72" t="n">
-        <v>79951.85400653176</v>
+        <v>79951.84357866758</v>
       </c>
       <c r="G72" t="n">
-        <v>4.909745674102614</v>
+        <v>4.90974741433437</v>
       </c>
       <c r="H72" t="n">
-        <v>72258.14730363266</v>
+        <v>72258.13515224327</v>
       </c>
       <c r="I72" t="n">
-        <v>87645.56070943087</v>
+        <v>87645.5520050919</v>
       </c>
       <c r="J72" t="n">
-        <v>72407.99088194186</v>
+        <v>72407.97876412037</v>
       </c>
       <c r="K72" t="n">
-        <v>87959.70988214115</v>
+        <v>87959.70124817746</v>
       </c>
       <c r="L72" t="n">
-        <v>72459.9849880742</v>
+        <v>72459.9728818993</v>
       </c>
       <c r="M72" t="n">
-        <v>87850.082644084</v>
+        <v>87850.07398556612</v>
       </c>
     </row>
     <row r="73">
@@ -4323,28 +4294,28 @@
         <v>0.0040377821474214</v>
       </c>
       <c r="F73" t="n">
-        <v>1508.834354258151</v>
+        <v>1508.806353782043</v>
       </c>
       <c r="G73" t="n">
-        <v>116.8902727940718</v>
+        <v>116.892468233414</v>
       </c>
       <c r="H73" t="n">
-        <v>-1947.916087672032</v>
+        <v>-1947.944862520859</v>
       </c>
       <c r="I73" t="n">
-        <v>4965.584796188335</v>
+        <v>4965.557570084944</v>
       </c>
       <c r="J73" t="n">
-        <v>4.61315333848198e-06</v>
+        <v>4.613154371909226e-06</v>
       </c>
       <c r="K73" t="n">
-        <v>5302.688593385555</v>
+        <v>5302.661442799035</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>5182.194132096382</v>
+        <v>5182.166954516754</v>
       </c>
     </row>
     <row r="74">
@@ -4364,28 +4335,28 @@
         <v>0.0039339098234216</v>
       </c>
       <c r="F74" t="n">
-        <v>1027.727175976232</v>
+        <v>1027.699067723495</v>
       </c>
       <c r="G74" t="n">
-        <v>158.2541108828027</v>
+        <v>158.2584746906115</v>
       </c>
       <c r="H74" t="n">
-        <v>-2159.998436839788</v>
+        <v>-2160.027259198964</v>
       </c>
       <c r="I74" t="n">
-        <v>4215.452788792251</v>
+        <v>4215.425394645954</v>
       </c>
       <c r="J74" t="n">
-        <v>4.61315333848198e-06</v>
+        <v>4.613154371909226e-06</v>
       </c>
       <c r="K74" t="n">
-        <v>4509.130316334367</v>
+        <v>4509.102987977155</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4404.385775807034</v>
+        <v>4404.358423986779</v>
       </c>
     </row>
   </sheetData>
@@ -4444,10 +4415,10 @@
         <v>1e-12</v>
       </c>
       <c r="C3" t="n">
-        <v>4.613255391624295e-06</v>
+        <v>4.613256425074404e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>31365961396.48196</v>
+        <v>31365961589.15795</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -4461,10 +4432,10 @@
         <v>1e-12</v>
       </c>
       <c r="C4" t="n">
-        <v>4.613255391624295e-06</v>
+        <v>4.613256425074404e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>33250686184.88422</v>
+        <v>33250686389.13776</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -4475,13 +4446,13 @@
         <v>0.0328</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0215456135241176</v>
+        <v>0.0215456075136319</v>
       </c>
       <c r="C5" t="n">
-        <v>99395.41775598888</v>
+        <v>99395.41229439391</v>
       </c>
       <c r="D5" t="n">
-        <v>4.137864971120066</v>
+        <v>4.137866150860734</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -4492,13 +4463,13 @@
         <v>0.0328</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0228167777907406</v>
+        <v>0.0228167717880635</v>
       </c>
       <c r="C6" t="n">
-        <v>105259.6231626276</v>
+        <v>105259.6190507404</v>
       </c>
       <c r="D6" t="n">
-        <v>4.05781669576276</v>
+        <v>4.057817788226942</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -4509,13 +4480,13 @@
         <v>0.0984</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0599113587817064</v>
+        <v>0.0599113530068952</v>
       </c>
       <c r="C7" t="n">
-        <v>276386.3989192446</v>
+        <v>276386.4341939602</v>
       </c>
       <c r="D7" t="n">
-        <v>2.47100266640157</v>
+        <v>2.471002919758664</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -4526,13 +4497,13 @@
         <v>0.0984</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0629148343097946</v>
+        <v>0.06291482855343331</v>
       </c>
       <c r="C8" t="n">
-        <v>290242.1985928095</v>
+        <v>290242.2370565811</v>
       </c>
       <c r="D8" t="n">
-        <v>2.170411218301673</v>
+        <v>2.170411430214863</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -4543,13 +4514,13 @@
         <v>0.296</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1622043888259011</v>
+        <v>0.1622043836794593</v>
       </c>
       <c r="C9" t="n">
-        <v>748290.2712962119</v>
+        <v>748290.4151844998</v>
       </c>
       <c r="D9" t="n">
-        <v>1.510068936628116</v>
+        <v>1.510068993815887</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -4560,13 +4531,13 @@
         <v>0.296</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1757497625873482</v>
+        <v>0.1757497575241135</v>
       </c>
       <c r="C10" t="n">
-        <v>810778.5398327742</v>
+        <v>810778.6981033854</v>
       </c>
       <c r="D10" t="n">
-        <v>1.158155496189594</v>
+        <v>1.158155536669651</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -4577,13 +4548,13 @@
         <v>0.888</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4165993509362544</v>
+        <v>0.4165993473525193</v>
       </c>
       <c r="C11" t="n">
-        <v>1921879.201853857</v>
+        <v>1921879.615855813</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6674809841406365</v>
+        <v>0.6674809939827709</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -4594,13 +4565,13 @@
         <v>0.888</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4394748175849425</v>
+        <v>0.4394748141417278</v>
       </c>
       <c r="C12" t="n">
-        <v>2027409.57170684</v>
+        <v>2027410.009997705</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6493065276464991</v>
+        <v>0.6493065367222959</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -4611,13 +4582,13 @@
         <v>2.664</v>
       </c>
       <c r="B13" t="n">
-        <v>0.806093871162752</v>
+        <v>0.8060938699716182</v>
       </c>
       <c r="C13" t="n">
-        <v>3718716.897296865</v>
+        <v>3718717.724859659</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2787648964321563</v>
+        <v>0.2787648985564837</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -4628,13 +4599,13 @@
         <v>2.664</v>
       </c>
       <c r="B14" t="n">
-        <v>0.824844496640454</v>
+        <v>0.8248444955645023</v>
       </c>
       <c r="C14" t="n">
-        <v>3805218.321378202</v>
+        <v>3805219.168850196</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2660093196317993</v>
+        <v>0.2660093216128417</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -4645,13 +4616,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9884073164579366</v>
+        <v>0.9884073163867244</v>
       </c>
       <c r="C15" t="n">
-        <v>4559775.381770477</v>
+        <v>4559776.402911606</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0715633101999392</v>
+        <v>0.0715633106446969</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -4662,13 +4633,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="n">
-        <v>0.992363234344773</v>
+        <v>0.9923632342978616</v>
       </c>
       <c r="C16" t="n">
-        <v>4578025.041290748</v>
+        <v>4578026.066632226</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0581216653015005</v>
+        <v>0.0581216656612799</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -4679,13 +4650,13 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9999982782702588</v>
+        <v>0.9999982782702482</v>
       </c>
       <c r="C17" t="n">
-        <v>4613247.448845283</v>
+        <v>4613248.482293565</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0007811668200994</v>
+        <v>0.0007811668248979</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -4696,13 +4667,13 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9999957762242776</v>
+        <v>0.9999957762242516</v>
       </c>
       <c r="C18" t="n">
-        <v>4613235.906268171</v>
+        <v>4613236.939713795</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0012141279346048</v>
+        <v>0.001214127942063</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -4792,25 +4763,25 @@
         <v>29568</v>
       </c>
       <c r="D3" t="n">
-        <v>2701.26299896267</v>
+        <v>2701.235265611467</v>
       </c>
       <c r="E3" t="n">
-        <v>5853.494238763038</v>
+        <v>5853.46721156689</v>
       </c>
       <c r="F3" t="n">
-        <v>10378.9912709319</v>
+        <v>10379.00020149188</v>
       </c>
       <c r="G3" t="n">
-        <v>55589663.31359267</v>
+        <v>55589675.73256401</v>
       </c>
       <c r="H3" t="n">
-        <v>2693.847764348127</v>
+        <v>2693.85059679535</v>
       </c>
       <c r="I3" t="n">
-        <v>5387.695528696253</v>
+        <v>5387.701193590705</v>
       </c>
       <c r="J3" t="n">
-        <v>10352.98862158629</v>
+        <v>10352.99751536408</v>
       </c>
     </row>
     <row r="4">
@@ -4824,25 +4795,25 @@
         <v>33529</v>
       </c>
       <c r="D4" t="n">
-        <v>2561.254286238433</v>
+        <v>2561.226521522954</v>
       </c>
       <c r="E4" t="n">
-        <v>5349.144913189301</v>
+        <v>5349.117773009969</v>
       </c>
       <c r="F4" t="n">
-        <v>9609.018465785206</v>
+        <v>9609.026840150467</v>
       </c>
       <c r="G4" t="n">
-        <v>56284188.9164738</v>
+        <v>56284201.49129799</v>
       </c>
       <c r="H4" t="n">
-        <v>2529.727392598303</v>
+        <v>2529.730052481105</v>
       </c>
       <c r="I4" t="n">
-        <v>5059.454785196608</v>
+        <v>5059.460104962208</v>
       </c>
       <c r="J4" t="n">
-        <v>9586.861009190659</v>
+        <v>9586.869351638161</v>
       </c>
     </row>
     <row r="5">
@@ -4856,25 +4827,25 @@
         <v>31110</v>
       </c>
       <c r="D5" t="n">
-        <v>2608.455807981186</v>
+        <v>2608.428053839778</v>
       </c>
       <c r="E5" t="n">
-        <v>5668.546712980773</v>
+        <v>5668.519644353428</v>
       </c>
       <c r="F5" t="n">
-        <v>10059.44027325704</v>
+        <v>10059.44897458613</v>
       </c>
       <c r="G5" t="n">
-        <v>55870713.95510441</v>
+        <v>55870726.43712916</v>
       </c>
       <c r="H5" t="n">
-        <v>2626.237620775931</v>
+        <v>2626.240382134445</v>
       </c>
       <c r="I5" t="n">
-        <v>5252.475241551862</v>
+        <v>5252.480764268892</v>
       </c>
       <c r="J5" t="n">
-        <v>10035.07273680425</v>
+        <v>10035.08140340484</v>
       </c>
     </row>
     <row r="6">
@@ -4888,25 +4859,25 @@
         <v>30257</v>
       </c>
       <c r="D6" t="n">
-        <v>2707.482741040725</v>
+        <v>2707.455009083082</v>
       </c>
       <c r="E6" t="n">
-        <v>5821.094993553303</v>
+        <v>5821.06795909919</v>
       </c>
       <c r="F6" t="n">
-        <v>10232.77964046084</v>
+        <v>10232.78846641301</v>
       </c>
       <c r="G6" t="n">
-        <v>55717046.59863082</v>
+        <v>55717059.04635361</v>
       </c>
       <c r="H6" t="n">
-        <v>2662.999538784118</v>
+        <v>2663.002338795969</v>
       </c>
       <c r="I6" t="n">
-        <v>5325.99907756824</v>
+        <v>5326.004677591935</v>
       </c>
       <c r="J6" t="n">
-        <v>10207.5320786284</v>
+        <v>10207.54086874415</v>
       </c>
     </row>
     <row r="7">
@@ -4920,25 +4891,25 @@
         <v>27297</v>
       </c>
       <c r="D7" t="n">
-        <v>2829.303768446247</v>
+        <v>2829.276063778547</v>
       </c>
       <c r="E7" t="n">
-        <v>5948.294092191311</v>
+        <v>5948.267086231748</v>
       </c>
       <c r="F7" t="n">
-        <v>10905.13895835222</v>
+        <v>10905.14826154524</v>
       </c>
       <c r="G7" t="n">
-        <v>55147274.22544287</v>
+        <v>55147286.54532284</v>
       </c>
       <c r="H7" t="n">
-        <v>2803.667865618317</v>
+        <v>2803.670813535929</v>
       </c>
       <c r="I7" t="n">
-        <v>5607.335731236637</v>
+        <v>5607.34162707186</v>
       </c>
       <c r="J7" t="n">
-        <v>10876.32197911385</v>
+        <v>10876.33124203749</v>
       </c>
     </row>
     <row r="8">
@@ -4952,25 +4923,25 @@
         <v>33491</v>
       </c>
       <c r="D8" t="n">
-        <v>2583.674290102529</v>
+        <v>2583.646530409142</v>
       </c>
       <c r="E8" t="n">
-        <v>5522.598482578126</v>
+        <v>5522.57138125534</v>
       </c>
       <c r="F8" t="n">
-        <v>9615.66553218921</v>
+        <v>9615.673911412876</v>
       </c>
       <c r="G8" t="n">
-        <v>56277931.79245336</v>
+        <v>56277944.36582117</v>
       </c>
       <c r="H8" t="n">
-        <v>2531.162142059462</v>
+        <v>2531.164803450829</v>
       </c>
       <c r="I8" t="n">
-        <v>5062.32428411892</v>
+        <v>5062.329606901657</v>
       </c>
       <c r="J8" t="n">
-        <v>9593.47626345438</v>
+        <v>9593.484610719604</v>
       </c>
     </row>
     <row r="9">
@@ -4984,25 +4955,25 @@
         <v>23171</v>
       </c>
       <c r="D9" t="n">
-        <v>3196.43635041882</v>
+        <v>3196.40872799506</v>
       </c>
       <c r="E9" t="n">
-        <v>6836.435427164475</v>
+        <v>6836.408620164663</v>
       </c>
       <c r="F9" t="n">
-        <v>12082.92276971725</v>
+        <v>12082.93288634417</v>
       </c>
       <c r="G9" t="n">
-        <v>54237862.87100397</v>
+        <v>54237874.98711154</v>
       </c>
       <c r="H9" t="n">
-        <v>3043.067846481089</v>
+        <v>3043.071046115896</v>
       </c>
       <c r="I9" t="n">
-        <v>6086.135692962176</v>
+        <v>6086.142092231796</v>
       </c>
       <c r="J9" t="n">
-        <v>12047.25133475439</v>
+        <v>12047.26140284417</v>
       </c>
     </row>
     <row r="10">
@@ -5016,25 +4987,25 @@
         <v>35706</v>
       </c>
       <c r="D10" t="n">
-        <v>2524.296704995831</v>
+        <v>2524.268932001212</v>
       </c>
       <c r="E10" t="n">
-        <v>5359.607217348491</v>
+        <v>5359.580079512684</v>
       </c>
       <c r="F10" t="n">
-        <v>9248.34903628499</v>
+        <v>9248.357145504118</v>
       </c>
       <c r="G10" t="n">
-        <v>56631089.9315818</v>
+        <v>56631102.58422212</v>
       </c>
       <c r="H10" t="n">
-        <v>2451.395720104811</v>
+        <v>2451.398297625743</v>
       </c>
       <c r="I10" t="n">
-        <v>4902.791440209618</v>
+        <v>4902.796595251487</v>
       </c>
       <c r="J10" t="n">
-        <v>9227.881760972068</v>
+        <v>9227.889840452082</v>
       </c>
     </row>
     <row r="11">
@@ -5048,25 +5019,25 @@
         <v>31713</v>
       </c>
       <c r="D11" t="n">
-        <v>2670.119783215604</v>
+        <v>2670.09204288793</v>
       </c>
       <c r="E11" t="n">
-        <v>5702.973245922924</v>
+        <v>5702.946185007636</v>
       </c>
       <c r="F11" t="n">
-        <v>9941.707584415351</v>
+        <v>9941.716200721065</v>
       </c>
       <c r="G11" t="n">
-        <v>55976773.99094353</v>
+        <v>55976786.49688964</v>
       </c>
       <c r="H11" t="n">
-        <v>2601.149777114228</v>
+        <v>2601.152512094122</v>
       </c>
       <c r="I11" t="n">
-        <v>5202.299554228456</v>
+        <v>5202.305024188242</v>
       </c>
       <c r="J11" t="n">
-        <v>9917.928401295192</v>
+        <v>9917.936983616552</v>
       </c>
     </row>
     <row r="12">
@@ -5080,25 +5051,25 @@
         <v>30509</v>
       </c>
       <c r="D12" t="n">
-        <v>2694.920014803064</v>
+        <v>2694.892280030936</v>
       </c>
       <c r="E12" t="n">
-        <v>5793.688168033835</v>
+        <v>5793.661127440299</v>
       </c>
       <c r="F12" t="n">
-        <v>10180.71171505606</v>
+        <v>10180.72050364322</v>
       </c>
       <c r="G12" t="n">
-        <v>55762899.31131759</v>
+        <v>55762911.76924735</v>
       </c>
       <c r="H12" t="n">
-        <v>2651.978735343093</v>
+        <v>2651.981523767116</v>
       </c>
       <c r="I12" t="n">
-        <v>5303.957470686189</v>
+        <v>5303.963047534228</v>
       </c>
       <c r="J12" t="n">
-        <v>10155.73022328968</v>
+        <v>10155.73897637476</v>
       </c>
     </row>
     <row r="13">
@@ -5112,25 +5083,25 @@
         <v>31098</v>
       </c>
       <c r="D13" t="n">
-        <v>2616.098897210277</v>
+        <v>2616.07114478074</v>
       </c>
       <c r="E13" t="n">
-        <v>5677.373157009905</v>
+        <v>5677.346090359788</v>
       </c>
       <c r="F13" t="n">
-        <v>10061.82259040306</v>
+        <v>10061.83129344949</v>
       </c>
       <c r="G13" t="n">
-        <v>55868582.09909897</v>
+        <v>55868594.58075526</v>
       </c>
       <c r="H13" t="n">
-        <v>2626.744274126991</v>
+        <v>2626.747036018225</v>
       </c>
       <c r="I13" t="n">
-        <v>5253.488548253978</v>
+        <v>5253.49407203645</v>
       </c>
       <c r="J13" t="n">
-        <v>10037.44307050854</v>
+        <v>10037.45173881128</v>
       </c>
     </row>
     <row r="14">
@@ -5144,25 +5115,25 @@
         <v>30145</v>
       </c>
       <c r="D14" t="n">
-        <v>2781.443469272219</v>
+        <v>2781.415753882803</v>
       </c>
       <c r="E14" t="n">
-        <v>5906.649017804092</v>
+        <v>5906.622002515655</v>
       </c>
       <c r="F14" t="n">
-        <v>10256.15885376707</v>
+        <v>10256.16769647739</v>
       </c>
       <c r="G14" t="n">
-        <v>55696542.4784701</v>
+        <v>55696554.9214818</v>
       </c>
       <c r="H14" t="n">
-        <v>2667.941974155964</v>
+        <v>2667.94477936454</v>
       </c>
       <c r="I14" t="n">
-        <v>5335.883948311933</v>
+        <v>5335.889558729078</v>
       </c>
       <c r="J14" t="n">
-        <v>10230.79134008712</v>
+        <v>10230.80014681041</v>
       </c>
     </row>
     <row r="15">
@@ -5176,25 +5147,25 @@
         <v>22988</v>
       </c>
       <c r="D15" t="n">
-        <v>3157.246781064177</v>
+        <v>3157.219149861626</v>
       </c>
       <c r="E15" t="n">
-        <v>6591.769715534965</v>
+        <v>6591.742853725394</v>
       </c>
       <c r="F15" t="n">
-        <v>12143.52688255139</v>
+        <v>12143.53704028941</v>
       </c>
       <c r="G15" t="n">
-        <v>54193782.31445217</v>
+        <v>54193794.42068493</v>
       </c>
       <c r="H15" t="n">
-        <v>3055.156273430573</v>
+        <v>3055.159485775761</v>
       </c>
       <c r="I15" t="n">
-        <v>6110.312546861144</v>
+        <v>6110.318971551526</v>
       </c>
       <c r="J15" t="n">
-        <v>12107.48188223652</v>
+        <v>12107.49199099524</v>
       </c>
     </row>
     <row r="16">
@@ -5208,25 +5179,25 @@
         <v>22866</v>
       </c>
       <c r="D16" t="n">
-        <v>3063.225625850177</v>
+        <v>3063.197973584673</v>
       </c>
       <c r="E16" t="n">
-        <v>6718.753487896955</v>
+        <v>6718.726654534032</v>
       </c>
       <c r="F16" t="n">
-        <v>12184.39495367838</v>
+        <v>12184.40513909946</v>
       </c>
       <c r="G16" t="n">
-        <v>54164195.77008808</v>
+        <v>54164207.86959048</v>
       </c>
       <c r="H16" t="n">
-        <v>3063.295721072496</v>
+        <v>3063.298941975912</v>
       </c>
       <c r="I16" t="n">
-        <v>6126.591442144992</v>
+        <v>6126.597883951824</v>
       </c>
       <c r="J16" t="n">
-        <v>12148.09688405139</v>
+        <v>12148.10702019406</v>
       </c>
     </row>
     <row r="17">
@@ -5240,25 +5211,25 @@
         <v>28320</v>
       </c>
       <c r="D17" t="n">
-        <v>2760.223162411009</v>
+        <v>2760.195442268055</v>
       </c>
       <c r="E17" t="n">
-        <v>5991.402378984619</v>
+        <v>5991.375382682211</v>
       </c>
       <c r="F17" t="n">
-        <v>10659.20285029993</v>
+        <v>10659.21198004747</v>
       </c>
       <c r="G17" t="n">
-        <v>55351027.90592658</v>
+        <v>55351040.27157597</v>
       </c>
       <c r="H17" t="n">
-        <v>2752.563833810761</v>
+        <v>2752.566727995023</v>
       </c>
       <c r="I17" t="n">
-        <v>5505.127667621527</v>
+        <v>5505.133455990043</v>
       </c>
       <c r="J17" t="n">
-        <v>10631.72031650358</v>
+        <v>10631.72940762795</v>
       </c>
     </row>
     <row r="18">
@@ -5272,25 +5243,25 @@
         <v>28760</v>
       </c>
       <c r="D18" t="n">
-        <v>2777.061251915209</v>
+        <v>2777.033535543858</v>
       </c>
       <c r="E18" t="n">
-        <v>5982.581085389858</v>
+        <v>5982.554087111112</v>
       </c>
       <c r="F18" t="n">
-        <v>10558.04102175932</v>
+        <v>10558.05007979063</v>
       </c>
       <c r="G18" t="n">
-        <v>55436365.14834657</v>
+        <v>55436377.53307361</v>
       </c>
       <c r="H18" t="n">
-        <v>2731.426905192325</v>
+        <v>2731.429777152153</v>
       </c>
       <c r="I18" t="n">
-        <v>5462.85381038465</v>
+        <v>5462.859554304306</v>
       </c>
       <c r="J18" t="n">
-        <v>10531.09772924071</v>
+        <v>10531.10674931772</v>
       </c>
     </row>
   </sheetData>
@@ -5310,7 +5281,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>LOO per-fold logL: positive Diff = 4PL better, negative = TCS better</t>
+          <t>LOO per-fold predictive quasi-score (quasi-logL): positive Diff = 4PL higher, negative = TCS higher</t>
         </is>
       </c>
     </row>
@@ -5322,17 +5293,17 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>4PL_logL</t>
+          <t>4PL_quasi_logL</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>TCS_logL</t>
+          <t>TCS_quasi_logL</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Diff(4PL-TCS)</t>
+          <t>Diff_quasi_logL(4PL-TCS)</t>
         </is>
       </c>
     </row>
@@ -5344,10 +5315,10 @@
         <v>-588.6824</v>
       </c>
       <c r="C3" t="n">
-        <v>-593.2918</v>
+        <v>-593.2903</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6093</v>
+        <v>4.6079</v>
       </c>
     </row>
     <row r="4">
@@ -5369,13 +5340,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-3658.4051</v>
+        <v>-3658.4014</v>
       </c>
       <c r="C5" t="n">
         <v>-3658.2192</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1859</v>
+        <v>-0.1822</v>
       </c>
     </row>
     <row r="6">
@@ -5383,13 +5354,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-3700.9755</v>
+        <v>-3700.9326</v>
       </c>
       <c r="C6" t="n">
-        <v>-3700.2936</v>
+        <v>-3700.2935</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6819</v>
+        <v>-0.6391</v>
       </c>
     </row>
     <row r="7">
@@ -5397,13 +5368,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-6448.4359</v>
+        <v>-6448.4356</v>
       </c>
       <c r="C7" t="n">
         <v>-6448.2228</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2131</v>
+        <v>-0.2128</v>
       </c>
     </row>
     <row r="8">
@@ -5411,13 +5382,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-8180.796</v>
+        <v>-8180.7483</v>
       </c>
       <c r="C8" t="n">
         <v>-8181.5184</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7224</v>
+        <v>0.7701</v>
       </c>
     </row>
     <row r="9">
@@ -5425,13 +5396,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-10400.9086</v>
+        <v>-10400.9457</v>
       </c>
       <c r="C9" t="n">
         <v>-10394.1582</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.7504</v>
+        <v>-6.7875</v>
       </c>
     </row>
     <row r="10">
@@ -5439,13 +5410,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-16769.0267</v>
+        <v>-16768.9001</v>
       </c>
       <c r="C10" t="n">
-        <v>-16772.4434</v>
+        <v>-16772.4432</v>
       </c>
       <c r="D10" t="n">
-        <v>3.4168</v>
+        <v>3.5431</v>
       </c>
     </row>
     <row r="11">
@@ -5453,13 +5424,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-21588.0014</v>
+        <v>-21587.9961</v>
       </c>
       <c r="C11" t="n">
-        <v>-21571.4568</v>
+        <v>-21571.4567</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.5446</v>
+        <v>-16.5394</v>
       </c>
     </row>
     <row r="12">
@@ -5467,13 +5438,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-20942.9045</v>
+        <v>-20943.2424</v>
       </c>
       <c r="C12" t="n">
-        <v>-20950.9438</v>
+        <v>-20950.9442</v>
       </c>
       <c r="D12" t="n">
-        <v>8.039300000000001</v>
+        <v>7.7018</v>
       </c>
     </row>
     <row r="13">
@@ -5481,13 +5452,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-15269.7034</v>
+        <v>-15269.6208</v>
       </c>
       <c r="C13" t="n">
-        <v>-15269.4476</v>
+        <v>-15269.4471</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2558</v>
+        <v>-0.1737</v>
       </c>
     </row>
     <row r="14">
@@ -5495,13 +5466,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-13996.5545</v>
+        <v>-13995.8473</v>
       </c>
       <c r="C14" t="n">
-        <v>-13982.7858</v>
+        <v>-13982.7857</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.7687</v>
+        <v>-13.0616</v>
       </c>
     </row>
     <row r="15">
@@ -5509,13 +5480,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-1470.6165</v>
+        <v>-1469.7297</v>
       </c>
       <c r="C15" t="n">
-        <v>-1488.1464</v>
+        <v>-1488.1465</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5299</v>
+        <v>18.4168</v>
       </c>
     </row>
     <row r="16">
@@ -5523,13 +5494,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-1029.0191</v>
+        <v>-1028.897</v>
       </c>
       <c r="C16" t="n">
         <v>-1023.9963</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.0228</v>
+        <v>-4.9007</v>
       </c>
     </row>
     <row r="17">
@@ -5537,13 +5508,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.7753</v>
+        <v>-0.779</v>
       </c>
       <c r="C17" t="n">
         <v>-0.74</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0354</v>
+        <v>-0.039</v>
       </c>
     </row>
     <row r="18">
@@ -5551,13 +5522,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.636</v>
+        <v>-1.6356</v>
       </c>
       <c r="C18" t="n">
         <v>-1.8316</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1956</v>
+        <v>0.196</v>
       </c>
     </row>
   </sheetData>
@@ -5616,10 +5587,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003711984493444581</v>
-      </c>
-      <c r="D3" t="n">
-        <v/>
+        <v>0.00371199061347928</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -5635,10 +5603,10 @@
         <v>15923.55769230769</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00714494022436581</v>
+        <v>0.007144945555596855</v>
       </c>
       <c r="D4" t="n">
-        <v>14.38487573176396</v>
+        <v>14.38488444788473</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5654,10 +5622,10 @@
         <v>28951.92307692307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009944921846721353</v>
+        <v>0.009944926536558037</v>
       </c>
       <c r="D5" t="n">
-        <v>9.347240998477309</v>
+        <v>9.347245375971605</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5673,10 +5641,10 @@
         <v>115807.6923076923</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02841074267282615</v>
+        <v>0.02841074317734373</v>
       </c>
       <c r="D6" t="n">
-        <v>3.987056413381473</v>
+        <v>3.987057367480108</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5692,10 +5660,10 @@
         <v>1757381.730769231</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3193184295032698</v>
+        <v>0.3193183755968379</v>
       </c>
       <c r="D7" t="n">
-        <v>1.052358554872003</v>
+        <v>1.052358666584465</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5711,10 +5679,10 @@
         <v>5182394.230769231</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6760250952972217</v>
+        <v>0.6760250157575626</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7526362353560315</v>
+        <v>0.7526362719157439</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5730,10 +5698,10 @@
         <v>13433692.30769231</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9458336608219731</v>
+        <v>0.9458336258201681</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8399183908980873</v>
+        <v>0.8399182972990686</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5749,10 +5717,10 @@
         <v>69484615.38461538</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9999997135401492</v>
+        <v>0.9999997135391843</v>
       </c>
       <c r="D10" t="n">
-        <v>72.60545412066264</v>
+        <v>72.60534855179603</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5845,16 +5813,16 @@
         <v>0.2106910664406849</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3638401192656471</v>
+        <v>0.3638525612765032</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3710732519827151</v>
+        <v>0.3710733253215138</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.007233132717067992</v>
+        <v>-0.007220764045010652</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0085490649253116</v>
+        <v>0.00853429971883457</v>
       </c>
     </row>
     <row r="4">
@@ -5874,16 +5842,16 @@
         <v>0.2384781563280824</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4198794219371372</v>
+        <v>0.4198728841541976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4281797086140443</v>
+        <v>0.4281797947456907</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.008300286676907076</v>
+        <v>-0.008306910591493077</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008501491659375249</v>
+        <v>0.008508341308054335</v>
       </c>
     </row>
     <row r="5">
@@ -5903,16 +5871,16 @@
         <v>0.9269920914207728</v>
       </c>
       <c r="F5" t="n">
-        <v>4.252055468957137</v>
+        <v>4.252646584838491</v>
       </c>
       <c r="G5" t="n">
-        <v>4.16435141511982</v>
+        <v>4.164352338219449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08770405383731639</v>
+        <v>0.08829424661904195</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009051550366535155</v>
+        <v>0.009111825022974251</v>
       </c>
     </row>
     <row r="6">
@@ -5932,16 +5900,16 @@
         <v>0.9230378252624778</v>
       </c>
       <c r="F6" t="n">
-        <v>4.16190689921909</v>
+        <v>4.162404760071983</v>
       </c>
       <c r="G6" t="n">
-        <v>4.080304453779577</v>
+        <v>4.08030535805121</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08160244543951389</v>
+        <v>0.08209940202077259</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008599791549099622</v>
+        <v>0.008651643914102336</v>
       </c>
     </row>
     <row r="7">
@@ -5961,16 +5929,16 @@
         <v>0.05653625973150411</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08562610603974516</v>
+        <v>0.08568012142005611</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08680702334278857</v>
+        <v>0.08680703300096689</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.001180917303043413</v>
+        <v>-0.001126911580910772</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005948669940832207</v>
+        <v>0.005674839339394167</v>
       </c>
     </row>
     <row r="8">
@@ -5990,16 +5958,16 @@
         <v>0.05673959670847872</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08596181801016724</v>
+        <v>0.08601589473094921</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08715047691260706</v>
+        <v>0.0871504866477249</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.001188658902439826</v>
+        <v>-0.001134591916775687</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005964176208371752</v>
+        <v>0.005691105351916415</v>
       </c>
     </row>
     <row r="9">
@@ -6019,16 +5987,16 @@
         <v>0.2962727233488889</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5435122725019448</v>
+        <v>0.5434591056322915</v>
       </c>
       <c r="G9" t="n">
-        <v>0.553945057031581</v>
+        <v>0.5539451713368708</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.01043278452963625</v>
+        <v>-0.01048606570457933</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008257336524513881</v>
+        <v>0.008299911303248086</v>
       </c>
     </row>
     <row r="10">
@@ -6048,16 +6016,16 @@
         <v>0.3092185375698673</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5726416008597153</v>
+        <v>0.5725768278810512</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5835306776663483</v>
+        <v>0.5835307985993361</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01088907680663298</v>
+        <v>-0.01095397071828486</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008180797779797189</v>
+        <v>0.008230014739764674</v>
       </c>
     </row>
     <row r="11">
@@ -6077,16 +6045,16 @@
         <v>0.09766295532959934</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1550477276964689</v>
+        <v>0.1551053024969272</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1578254345409578</v>
+        <v>0.1578254601085056</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.002777706844488914</v>
+        <v>-0.0027201576115784</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007711587931713004</v>
+        <v>0.007550419053471313</v>
       </c>
     </row>
     <row r="12">
@@ -6106,16 +6074,16 @@
         <v>0.1006462696609974</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1602071652256157</v>
+        <v>0.1602644336994927</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1631023390333727</v>
+        <v>0.1631023657830398</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.002895173807757029</v>
+        <v>-0.002837932083547157</v>
       </c>
       <c r="I12" t="n">
-        <v>0.007778253360840037</v>
+        <v>0.007623107198234336</v>
       </c>
     </row>
     <row r="13">
@@ -6135,16 +6103,16 @@
         <v>0.1185311629915233</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1915072737667291</v>
+        <v>0.1915614479930444</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1951090010004934</v>
+        <v>0.1951090349202139</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.003601727233764229</v>
+        <v>-0.003547586927169472</v>
       </c>
       <c r="I13" t="n">
-        <v>0.008092031397175736</v>
+        <v>0.007969269578639748</v>
       </c>
     </row>
     <row r="14">
@@ -6164,16 +6132,16 @@
         <v>0.1180170365692051</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1905985182451726</v>
+        <v>0.1906528096464346</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1941798925290421</v>
+        <v>0.1941799262406262</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.003581374283869454</v>
+        <v>-0.003527116594191582</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008084736372069079</v>
+        <v>0.007961121939037641</v>
       </c>
     </row>
     <row r="15">
@@ -6193,16 +6161,16 @@
         <v>0.2866570240223245</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5222319027009149</v>
+        <v>0.5221870983677387</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5323200510247096</v>
+        <v>0.532320160485619</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.01008814832379468</v>
+        <v>-0.01013306211788034</v>
       </c>
       <c r="I15" t="n">
-        <v>0.008309426177060819</v>
+        <v>0.008346776914663456</v>
       </c>
     </row>
     <row r="16">
@@ -6222,16 +6190,16 @@
         <v>0.2889233862063423</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5272207693326456</v>
+        <v>0.527174014336161</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5373905630979481</v>
+        <v>0.537390673694741</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01016979376530247</v>
+        <v>-0.01021665935858007</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008297525173516618</v>
+        <v>0.008336130367353034</v>
       </c>
     </row>
     <row r="17">
@@ -6251,16 +6219,16 @@
         <v>0.0891853380125307</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1404801085751617</v>
+        <v>0.1405381923621316</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1429248636643105</v>
+        <v>0.1429248858938692</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00244475508914882</v>
+        <v>-0.002386693531737621</v>
       </c>
       <c r="I17" t="n">
-        <v>0.007492952391584096</v>
+        <v>0.007313490929857891</v>
       </c>
     </row>
     <row r="18">
@@ -6280,16 +6248,16 @@
         <v>0.08879756996380084</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1398170697126115</v>
+        <v>0.1398751634214015</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1422466295060952</v>
+        <v>0.1422466515837176</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.002429559793483721</v>
+        <v>-0.002371488162316138</v>
       </c>
       <c r="I18" t="n">
-        <v>0.007481788762581543</v>
+        <v>0.007301445169485166</v>
       </c>
     </row>
     <row r="19">
@@ -6309,16 +6277,16 @@
         <v>0.908920415707608</v>
       </c>
       <c r="F19" t="n">
-        <v>3.875347495899186</v>
+        <v>3.875578148067564</v>
       </c>
       <c r="G19" t="n">
-        <v>3.811941386613642</v>
+        <v>3.811942230767245</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06340610928554336</v>
+        <v>0.06363591730031981</v>
       </c>
       <c r="I19" t="n">
-        <v>0.007164436850417566</v>
+        <v>0.007190188160192013</v>
       </c>
     </row>
     <row r="20">
@@ -6338,16 +6306,16 @@
         <v>0.8969750377321517</v>
       </c>
       <c r="F20" t="n">
-        <v>3.666894350560329</v>
+        <v>3.666958251577081</v>
       </c>
       <c r="G20" t="n">
-        <v>3.615572158223876</v>
+        <v>3.615572958387328</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0513221923364533</v>
+        <v>0.05138529318975316</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00612136393926821</v>
+        <v>0.006128835978337799</v>
       </c>
     </row>
     <row r="21">
@@ -6367,16 +6335,16 @@
         <v>0.2863305178695573</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5215145242578629</v>
+        <v>0.5214699999024331</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5315908895912389</v>
+        <v>0.5315909988888033</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01007636533337597</v>
+        <v>-0.0101209989863702</v>
       </c>
       <c r="I21" t="n">
-        <v>0.008311121294739043</v>
+        <v>0.008348290106018785</v>
       </c>
     </row>
     <row r="22">
@@ -6396,133 +6364,37 @@
         <v>0.2951619719410735</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5410387989657814</v>
+        <v>0.5409866095310533</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5514320132604437</v>
+        <v>0.5514321270027676</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.01039321429466222</v>
+        <v>-0.01044551747171429</v>
       </c>
       <c r="I22" t="n">
-        <v>0.008263565026945807</v>
+        <v>0.008305549341999674</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
-      <c r="C23" t="n">
-        <v/>
-      </c>
-      <c r="D23" t="n">
-        <v/>
-      </c>
-      <c r="E23" t="n">
-        <v/>
-      </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
-      <c r="G23" t="n">
-        <v/>
-      </c>
-      <c r="H23" t="n">
-        <v/>
-      </c>
-      <c r="I23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
-        <v/>
-      </c>
-      <c r="C24" t="n">
-        <v/>
-      </c>
-      <c r="D24" t="n">
-        <v/>
-      </c>
-      <c r="E24" t="n">
-        <v/>
-      </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
-      <c r="G24" t="n">
-        <v/>
-      </c>
-      <c r="H24" t="n">
-        <v/>
-      </c>
-      <c r="I24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
-        <v/>
-      </c>
-      <c r="C25" t="n">
-        <v/>
-      </c>
-      <c r="D25" t="n">
-        <v/>
-      </c>
-      <c r="E25" t="n">
-        <v/>
-      </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
-      <c r="G25" t="n">
-        <v/>
-      </c>
-      <c r="H25" t="n">
-        <v/>
-      </c>
-      <c r="I25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
-        <v/>
-      </c>
-      <c r="C26" t="n">
-        <v/>
-      </c>
-      <c r="D26" t="n">
-        <v/>
-      </c>
-      <c r="E26" t="n">
-        <v/>
-      </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
-      <c r="G26" t="n">
-        <v/>
-      </c>
-      <c r="H26" t="n">
-        <v/>
-      </c>
-      <c r="I26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -6541,16 +6413,7 @@
         <v>0.9999999466406074</v>
       </c>
       <c r="F27" t="n">
-        <v>38.37471908556955</v>
-      </c>
-      <c r="G27" t="n">
-        <v/>
-      </c>
-      <c r="H27" t="n">
-        <v/>
-      </c>
-      <c r="I27" t="n">
-        <v/>
+        <v>38.77559617654099</v>
       </c>
     </row>
     <row r="28">
@@ -6570,16 +6433,7 @@
         <v>0.9999999203000804</v>
       </c>
       <c r="F28" t="n">
-        <v>37.02033395007616</v>
-      </c>
-      <c r="G28" t="n">
-        <v/>
-      </c>
-      <c r="H28" t="n">
-        <v/>
-      </c>
-      <c r="I28" t="n">
-        <v/>
+        <v>37.39080826607475</v>
       </c>
     </row>
     <row r="29">
@@ -6599,16 +6453,16 @@
         <v>0.3412250216193241</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6471511060018693</v>
+        <v>0.6470560440162054</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6591248713234392</v>
+        <v>0.6591250091908519</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.01197376532156991</v>
+        <v>-0.01206896517464651</v>
       </c>
       <c r="I29" t="n">
-        <v>0.007962001821911813</v>
+        <v>0.00802589217967925</v>
       </c>
     </row>
     <row r="30">
@@ -6628,16 +6482,16 @@
         <v>0.3438827957621401</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6535056685811489</v>
+        <v>0.6534079956566384</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6655663948513468</v>
+        <v>0.665566534161774</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01206072627019794</v>
+        <v>-0.0121585385051356</v>
       </c>
       <c r="I30" t="n">
-        <v>0.007942026798442664</v>
+        <v>0.008007032183786511</v>
       </c>
     </row>
     <row r="31">
@@ -6657,16 +6511,7 @@
         <v>0.9999999893311496</v>
       </c>
       <c r="F31" t="n">
-        <v>44.1457618420209</v>
-      </c>
-      <c r="G31" t="n">
-        <v/>
-      </c>
-      <c r="H31" t="n">
-        <v/>
-      </c>
-      <c r="I31" t="n">
-        <v/>
+        <v>44.69000863253624</v>
       </c>
     </row>
     <row r="32">
@@ -6686,16 +6531,7 @@
         <v>0.9999999929925677</v>
       </c>
       <c r="F32" t="n">
-        <v>45.74844854021195</v>
-      </c>
-      <c r="G32" t="n">
-        <v/>
-      </c>
-      <c r="H32" t="n">
-        <v/>
-      </c>
-      <c r="I32" t="n">
-        <v/>
+        <v>46.33650066628223</v>
       </c>
     </row>
     <row r="33">
@@ -6715,16 +6551,16 @@
         <v>0.9684001270826436</v>
       </c>
       <c r="F33" t="n">
-        <v>5.70966851082085</v>
+        <v>5.712395289297729</v>
       </c>
       <c r="G33" t="n">
-        <v>5.498704143599478</v>
+        <v>5.49870536561752</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2109643672213721</v>
+        <v>0.2136899236802092</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01635054171373429</v>
+        <v>0.01655780262215301</v>
       </c>
     </row>
     <row r="34">
@@ -6744,16 +6580,16 @@
         <v>0.9719385044096266</v>
       </c>
       <c r="F34" t="n">
-        <v>5.920488876019058</v>
+        <v>5.923624500225335</v>
       </c>
       <c r="G34" t="n">
-        <v>5.687930219720489</v>
+        <v>5.687931484128492</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2325586562985693</v>
+        <v>0.2356930160968433</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0174033096856373</v>
+        <v>0.01763316439071116</v>
       </c>
     </row>
     <row r="35">
@@ -6773,16 +6609,16 @@
         <v>0.9971122343547186</v>
       </c>
       <c r="F35" t="n">
-        <v>10.16953360263497</v>
+        <v>10.18653359964958</v>
       </c>
       <c r="G35" t="n">
-        <v>9.311230821822139</v>
+        <v>9.311232897912994</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8583027808128261</v>
+        <v>0.875300701736581</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03829394289682475</v>
+        <v>0.03901923241066163</v>
       </c>
     </row>
     <row r="36">
@@ -6802,16 +6638,16 @@
         <v>0.9982000642767084</v>
       </c>
       <c r="F36" t="n">
-        <v>11.10693310341982</v>
+        <v>11.12847062307972</v>
       </c>
       <c r="G36" t="n">
-        <v>10.06449131250654</v>
+        <v>10.06449355734098</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04244179091328</v>
+        <v>1.063977065738746</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04280232681487695</v>
+        <v>0.04364355749742166</v>
       </c>
     </row>
     <row r="37">
@@ -6831,16 +6667,16 @@
         <v>0.9999538201831938</v>
       </c>
       <c r="F37" t="n">
-        <v>19.10231640968601</v>
+        <v>19.18501752448085</v>
       </c>
       <c r="G37" t="n">
-        <v>15.90112800003245</v>
+        <v>15.90113155237447</v>
       </c>
       <c r="H37" t="n">
-        <v>3.201188409653565</v>
+        <v>3.283885972106377</v>
       </c>
       <c r="I37" t="n">
-        <v>0.07965810086368874</v>
+        <v>0.08153416966294902</v>
       </c>
     </row>
     <row r="38">
@@ -6860,16 +6696,16 @@
         <v>0.9999534039058561</v>
       </c>
       <c r="F38" t="n">
-        <v>19.08098189284852</v>
+        <v>19.16346553792101</v>
       </c>
       <c r="G38" t="n">
-        <v>15.8868288397913</v>
+        <v>15.88683238893052</v>
       </c>
       <c r="H38" t="n">
-        <v>3.194153053057228</v>
+        <v>3.276633148990491</v>
       </c>
       <c r="I38" t="n">
-        <v>0.07956350280583835</v>
+        <v>0.0814367364162607</v>
       </c>
     </row>
     <row r="39">
@@ -6889,16 +6725,16 @@
         <v>0.9990444931181928</v>
       </c>
       <c r="F39" t="n">
-        <v>12.39412388703191</v>
+        <v>12.42278114770057</v>
       </c>
       <c r="G39" t="n">
-        <v>11.07354683911568</v>
+        <v>11.07354930999624</v>
       </c>
       <c r="H39" t="n">
-        <v>1.320577047916228</v>
+        <v>1.349231837704336</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0489290859008138</v>
+        <v>0.04993199043219643</v>
       </c>
     </row>
     <row r="40">
@@ -6918,16 +6754,16 @@
         <v>0.9989296602098154</v>
       </c>
       <c r="F40" t="n">
-        <v>12.16073083304113</v>
+        <v>12.18802042400897</v>
       </c>
       <c r="G40" t="n">
-        <v>10.89271052050401</v>
+        <v>10.89271295087395</v>
       </c>
       <c r="H40" t="n">
-        <v>1.268020312537123</v>
+        <v>1.295307473135013</v>
       </c>
       <c r="I40" t="n">
-        <v>0.04782371367711669</v>
+        <v>0.0487971142363095</v>
       </c>
     </row>
     <row r="41">
@@ -6947,16 +6783,16 @@
         <v>0.8659939722722469</v>
       </c>
       <c r="F41" t="n">
-        <v>3.225613234287659</v>
+        <v>3.225399319109697</v>
       </c>
       <c r="G41" t="n">
-        <v>3.196640751008244</v>
+        <v>3.196641457323714</v>
       </c>
       <c r="H41" t="n">
-        <v>0.02897248327941426</v>
+        <v>0.02875786178598272</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0039184607159225</v>
+        <v>0.003889562399742696</v>
       </c>
     </row>
     <row r="42">
@@ -6976,16 +6812,16 @@
         <v>0.8969808401406735</v>
       </c>
       <c r="F42" t="n">
-        <v>3.66698938179688</v>
+        <v>3.66705335358653</v>
       </c>
       <c r="G42" t="n">
-        <v>3.615661902787468</v>
+        <v>3.615662702971024</v>
       </c>
       <c r="H42" t="n">
-        <v>0.05132747900941181</v>
+        <v>0.05139065061550552</v>
       </c>
       <c r="I42" t="n">
-        <v>0.006121839186038369</v>
+        <v>0.006129319410686951</v>
       </c>
     </row>
     <row r="43">
@@ -7005,16 +6841,16 @@
         <v>0.9999895677777672</v>
       </c>
       <c r="F43" t="n">
-        <v>22.77332137895795</v>
+        <v>22.89782523229472</v>
       </c>
       <c r="G43" t="n">
-        <v>18.27156795761822</v>
+        <v>18.27157204097098</v>
       </c>
       <c r="H43" t="n">
-        <v>4.501753421339728</v>
+        <v>4.626253191323734</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0956505574586668</v>
+        <v>0.0980183217077899</v>
       </c>
     </row>
     <row r="44">
@@ -7034,16 +6870,16 @@
         <v>0.9999914714452309</v>
       </c>
       <c r="F44" t="n">
-        <v>23.29192795621097</v>
+        <v>23.42304265863002</v>
       </c>
       <c r="G44" t="n">
-        <v>18.59260911252091</v>
+        <v>18.59261326781653</v>
       </c>
       <c r="H44" t="n">
-        <v>4.699318843690055</v>
+        <v>4.830429390813489</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09786509926454867</v>
+        <v>0.100302873426608</v>
       </c>
     </row>
     <row r="45">
@@ -7063,16 +6899,16 @@
         <v>0.9800109292641285</v>
       </c>
       <c r="F45" t="n">
-        <v>6.528476774182531</v>
+        <v>6.532936007379744</v>
       </c>
       <c r="G45" t="n">
-        <v>6.228438312527934</v>
+        <v>6.228439698019216</v>
       </c>
       <c r="H45" t="n">
-        <v>0.300038461654597</v>
+        <v>0.3044963093605277</v>
       </c>
       <c r="I45" t="n">
-        <v>0.02043269591615404</v>
+        <v>0.02072914003997206</v>
       </c>
     </row>
     <row r="46">
@@ -7092,16 +6928,16 @@
         <v>0.9853753480289698</v>
       </c>
       <c r="F46" t="n">
-        <v>7.096278508596043</v>
+        <v>7.102169668579256</v>
       </c>
       <c r="G46" t="n">
-        <v>6.726345308564113</v>
+        <v>6.726346805595306</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3699332000319302</v>
+        <v>0.3758228629839504</v>
       </c>
       <c r="I46" t="n">
-        <v>0.02325149316313557</v>
+        <v>0.02361178778037021</v>
       </c>
     </row>
     <row r="47">
@@ -7121,16 +6957,16 @@
         <v>0.9997838788642888</v>
       </c>
       <c r="F47" t="n">
-        <v>15.56579500129187</v>
+        <v>15.6164364631482</v>
       </c>
       <c r="G47" t="n">
-        <v>13.44200995762954</v>
+        <v>13.44201295908777</v>
       </c>
       <c r="H47" t="n">
-        <v>2.123785043662336</v>
+        <v>2.174423504060432</v>
       </c>
       <c r="I47" t="n">
-        <v>0.06370709378714534</v>
+        <v>0.06511762881433159</v>
       </c>
     </row>
     <row r="48">
@@ -7150,16 +6986,16 @@
         <v>0.9999122068639951</v>
       </c>
       <c r="F48" t="n">
-        <v>17.59825180853997</v>
+        <v>17.66633883398399</v>
       </c>
       <c r="G48" t="n">
-        <v>14.8774509150562</v>
+        <v>14.87745423807733</v>
       </c>
       <c r="H48" t="n">
-        <v>2.720800893483773</v>
+        <v>2.788884595906659</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0729410015307006</v>
+        <v>0.07461793270977868</v>
       </c>
     </row>
     <row r="49">
@@ -7179,16 +7015,16 @@
         <v>0.999568855376163</v>
       </c>
       <c r="F49" t="n">
-        <v>14.06507738101773</v>
+        <v>14.10452497270607</v>
       </c>
       <c r="G49" t="n">
-        <v>12.34158735863536</v>
+        <v>12.34159011357925</v>
       </c>
       <c r="H49" t="n">
-        <v>1.72349002238237</v>
+        <v>1.762934859126826</v>
       </c>
       <c r="I49" t="n">
-        <v>0.05677110416913123</v>
+        <v>0.05798734548664952</v>
       </c>
     </row>
     <row r="50">
@@ -7208,16 +7044,16 @@
         <v>0.9995887676390042</v>
       </c>
       <c r="F50" t="n">
-        <v>14.16629987605381</v>
+        <v>14.20645762712022</v>
       </c>
       <c r="G50" t="n">
-        <v>12.41693247535637</v>
+        <v>12.41693524717852</v>
       </c>
       <c r="H50" t="n">
-        <v>1.749367400697436</v>
+        <v>1.789522379941699</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05724211143660107</v>
+        <v>0.05847138398847163</v>
       </c>
     </row>
     <row r="51">
@@ -7237,16 +7073,16 @@
         <v>0.5176717745405706</v>
       </c>
       <c r="F51" t="n">
-        <v>1.139846099394583</v>
+        <v>1.139555614688684</v>
       </c>
       <c r="G51" t="n">
-        <v>1.155884771156534</v>
+        <v>1.155885020306876</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.01603867176195117</v>
+        <v>-0.01632940561819129</v>
       </c>
       <c r="I51" t="n">
-        <v>0.006068324524529843</v>
+        <v>0.00617911025777839</v>
       </c>
     </row>
     <row r="52">
@@ -7266,16 +7102,16 @@
         <v>0.5247694755295773</v>
       </c>
       <c r="F52" t="n">
-        <v>1.163412442782844</v>
+        <v>1.16311360324903</v>
       </c>
       <c r="G52" t="n">
-        <v>1.179506968953567</v>
+        <v>1.179507223395695</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.01609452617072304</v>
+        <v>-0.01639362014666479</v>
       </c>
       <c r="I52" t="n">
-        <v>0.005966806898930602</v>
+        <v>0.006078469815769066</v>
       </c>
     </row>
     <row r="53">
@@ -7295,16 +7131,16 @@
         <v>0.6643772692472614</v>
       </c>
       <c r="F53" t="n">
-        <v>1.720051750079273</v>
+        <v>1.719603513990315</v>
       </c>
       <c r="G53" t="n">
-        <v>1.733717806743277</v>
+        <v>1.733718185338352</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.01366605666400367</v>
+        <v>-0.01411467134803712</v>
       </c>
       <c r="I53" t="n">
-        <v>0.003436896339387346</v>
+        <v>0.003550180695284288</v>
       </c>
     </row>
     <row r="54">
@@ -7324,16 +7160,16 @@
         <v>0.686187545130247</v>
       </c>
       <c r="F54" t="n">
-        <v>1.828429503324183</v>
+        <v>1.827964777907307</v>
       </c>
       <c r="G54" t="n">
-        <v>1.840783115723575</v>
+        <v>1.840783518303156</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.01235361239939214</v>
+        <v>-0.01281874039584951</v>
       </c>
       <c r="I54" t="n">
-        <v>0.002924401786386532</v>
+        <v>0.003034893879061196</v>
       </c>
     </row>
     <row r="55">
@@ -7353,16 +7189,16 @@
         <v>0.3168410560066339</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5900579128512629</v>
+        <v>0.5899861268128365</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6012112012061024</v>
+        <v>0.6012113260998377</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.01115328835483953</v>
+        <v>-0.01122519928700128</v>
       </c>
       <c r="I55" t="n">
-        <v>0.008132424603361887</v>
+        <v>0.008185354003508116</v>
       </c>
     </row>
     <row r="56">
@@ -7382,16 +7218,16 @@
         <v>0.3025717897803709</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5576160262967946</v>
+        <v>0.5575572610129015</v>
       </c>
       <c r="G56" t="n">
-        <v>0.568271977827839</v>
+        <v>0.5682720953426105</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.01065595153104437</v>
+        <v>-0.01071483432970899</v>
       </c>
       <c r="I56" t="n">
-        <v>0.008220993777655033</v>
+        <v>0.008266854838367033</v>
       </c>
     </row>
     <row r="57">
@@ -7411,16 +7247,16 @@
         <v>0.2595353119189138</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4637676631277915</v>
+        <v>0.4637451819115493</v>
       </c>
       <c r="G57" t="n">
-        <v>0.472860638275645</v>
+        <v>0.4728607344166032</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.009092975147853455</v>
+        <v>-0.009115552505053859</v>
       </c>
       <c r="I57" t="n">
-        <v>0.008432700562444051</v>
+        <v>0.008453841871263856</v>
       </c>
     </row>
     <row r="58">
@@ -7440,16 +7276,16 @@
         <v>0.266110322648404</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4777355997147916</v>
+        <v>0.4777078849452398</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4870727149670013</v>
+        <v>0.4870728142917138</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.009337115252209705</v>
+        <v>-0.009364929346474038</v>
       </c>
       <c r="I58" t="n">
-        <v>0.008406196696460644</v>
+        <v>0.008431480618973142</v>
       </c>
     </row>
     <row r="59">
@@ -7469,16 +7305,16 @@
         <v>0.9999585115158668</v>
       </c>
       <c r="F59" t="n">
-        <v>19.35772454933663</v>
+        <v>19.44305190162974</v>
       </c>
       <c r="G59" t="n">
-        <v>16.07182613557027</v>
+        <v>16.07182972615348</v>
       </c>
       <c r="H59" t="n">
-        <v>3.285898413766368</v>
+        <v>3.371222175476262</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08078908019104425</v>
+        <v>0.08269911287899756</v>
       </c>
     </row>
     <row r="60">
@@ -7498,16 +7334,16 @@
         <v>0.9999539617978218</v>
       </c>
       <c r="F60" t="n">
-        <v>19.10962027656709</v>
+        <v>19.1923959094623</v>
       </c>
       <c r="G60" t="n">
-        <v>15.90602187361036</v>
+        <v>15.90602542704922</v>
       </c>
       <c r="H60" t="n">
-        <v>3.203598402956725</v>
+        <v>3.286370482413083</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07969048201284323</v>
+        <v>0.08156752150442914</v>
       </c>
     </row>
     <row r="61">
@@ -7527,16 +7363,16 @@
         <v>0.9738706191312665</v>
       </c>
       <c r="F61" t="n">
-        <v>6.047635277488588</v>
+        <v>6.051029905910092</v>
       </c>
       <c r="G61" t="n">
-        <v>5.801601548873394</v>
+        <v>5.801602838745762</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2460337286151946</v>
+        <v>0.2494270671643299</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01803769336703598</v>
+        <v>0.01828130442716513</v>
       </c>
     </row>
     <row r="62">
@@ -7556,16 +7392,16 @@
         <v>0.978026424452201</v>
       </c>
       <c r="F62" t="n">
-        <v>6.35795093025338</v>
+        <v>6.362017156250807</v>
       </c>
       <c r="G62" t="n">
-        <v>6.077613271030492</v>
+        <v>6.077614622734331</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2803376592228881</v>
+        <v>0.2844025335164755</v>
       </c>
       <c r="I62" t="n">
-        <v>0.01958411005020977</v>
+        <v>0.01986167761159363</v>
       </c>
     </row>
     <row r="63">
@@ -7585,16 +7421,16 @@
         <v>0.7308584339589387</v>
       </c>
       <c r="F63" t="n">
-        <v>2.077159605156943</v>
+        <v>2.076674866582541</v>
       </c>
       <c r="G63" t="n">
-        <v>2.085465434899139</v>
+        <v>2.085465892291851</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.008305829742196291</v>
+        <v>-0.008791025709309785</v>
       </c>
       <c r="I63" t="n">
-        <v>0.001733127907087295</v>
+        <v>0.001834584582503851</v>
       </c>
     </row>
     <row r="64">
@@ -7614,16 +7450,16 @@
         <v>0.7179658519502181</v>
       </c>
       <c r="F64" t="n">
-        <v>2.001213634619589</v>
+        <v>2.000732291284129</v>
       </c>
       <c r="G64" t="n">
-        <v>2.010908313433728</v>
+        <v>2.010908754124338</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.009694678814138769</v>
+        <v>-0.01017646284020968</v>
       </c>
       <c r="I64" t="n">
-        <v>0.002098816417699989</v>
+        <v>0.002203383147610649</v>
       </c>
     </row>
     <row r="65">
@@ -7643,16 +7479,16 @@
         <v>0.3880655224327179</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7632277412369111</v>
+        <v>0.7630847445716579</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7766503870567735</v>
+        <v>0.7766505512519629</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.01342264581986241</v>
+        <v>-0.01356580668030505</v>
       </c>
       <c r="I65" t="n">
-        <v>0.007571415623053801</v>
+        <v>0.007652883518372053</v>
       </c>
     </row>
     <row r="66">
@@ -7672,16 +7508,16 @@
         <v>0.3873361701360253</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7613507698150253</v>
+        <v>0.7612085486348994</v>
       </c>
       <c r="G66" t="n">
-        <v>0.7747523537516139</v>
+        <v>0.7747525175216103</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.01340158393658863</v>
+        <v>-0.01354396888671094</v>
       </c>
       <c r="I66" t="n">
-        <v>0.007578113134904377</v>
+        <v>0.007659339213568858</v>
       </c>
     </row>
     <row r="67">
@@ -7701,16 +7537,16 @@
         <v>0.1518208154702774</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2515309899446156</v>
+        <v>0.2515744870378085</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2564520329834443</v>
+        <v>0.2564520806450797</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.004921043038828621</v>
+        <v>-0.004877593607271136</v>
       </c>
       <c r="I67" t="n">
-        <v>0.008414646157915096</v>
+        <v>0.008339631097576627</v>
       </c>
     </row>
     <row r="68">
@@ -7730,16 +7566,16 @@
         <v>0.1492695571555508</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2468463647170269</v>
+        <v>0.2468908792610106</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2516663430223008</v>
+        <v>0.2516663896118579</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.004819978305273975</v>
+        <v>-0.004775510350847306</v>
       </c>
       <c r="I68" t="n">
-        <v>0.008398402615631739</v>
+        <v>0.008320172450708152</v>
       </c>
     </row>
     <row r="69">
@@ -7759,16 +7595,16 @@
         <v>0.05854430417289479</v>
       </c>
       <c r="F69" t="n">
-        <v>0.08894457029913634</v>
+        <v>0.08899916817337289</v>
       </c>
       <c r="G69" t="n">
-        <v>0.09020203108761471</v>
+        <v>0.09020204150633419</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.001257460788478368</v>
+        <v>-0.001202873332961304</v>
       </c>
       <c r="I69" t="n">
-        <v>0.006096875367757493</v>
+        <v>0.005830419314080126</v>
       </c>
     </row>
     <row r="70">
@@ -7788,16 +7624,16 @@
         <v>0.05955716914968079</v>
       </c>
       <c r="F70" t="n">
-        <v>0.09062108880753532</v>
+        <v>0.09067596118810112</v>
       </c>
       <c r="G70" t="n">
-        <v>0.09191723386525298</v>
+        <v>0.09191724466820808</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.001296145057717663</v>
+        <v>-0.001241283480106964</v>
       </c>
       <c r="I70" t="n">
-        <v>0.006167670425512028</v>
+        <v>0.005904829459140615</v>
       </c>
     </row>
     <row r="71">
@@ -7817,16 +7653,16 @@
         <v>0.02220687309084657</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02993871376235433</v>
+        <v>0.02997200927993432</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02985791687044945</v>
+        <v>0.02985791377102931</v>
       </c>
       <c r="H71" t="n">
-        <v>8.079689190488779e-05</v>
+        <v>0.0001140955089050134</v>
       </c>
       <c r="I71" t="n">
-        <v>0.001173633540639818</v>
+        <v>0.001656398921046298</v>
       </c>
     </row>
     <row r="72">
@@ -7846,16 +7682,16 @@
         <v>0.02082978757070253</v>
       </c>
       <c r="F72" t="n">
-        <v>0.02774385220157749</v>
+        <v>0.0277756910875882</v>
       </c>
       <c r="G72" t="n">
-        <v>0.02761538630580971</v>
+        <v>0.02761538270402334</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0001284658957677737</v>
+        <v>0.0001603083835648549</v>
       </c>
       <c r="I72" t="n">
-        <v>0.00201563935119986</v>
+        <v>0.002513807225627218</v>
       </c>
     </row>
     <row r="73">
@@ -7875,16 +7711,16 @@
         <v>0.004037782147421454</v>
       </c>
       <c r="F73" t="n">
-        <v>0.001174932743504848</v>
+        <v>0.001178038108967478</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0005211516866252</v>
+        <v>0.0005211420152551724</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0006537810568796478</v>
+        <v>0.0006568960937123061</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3530488594364392</v>
+        <v>0.3542032518420792</v>
       </c>
     </row>
     <row r="74">
@@ -7904,16 +7740,16 @@
         <v>0.003933909823421677</v>
       </c>
       <c r="F74" t="n">
-        <v>0.001011053741889413</v>
+        <v>0.001013798221159595</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0003549771713767124</v>
+        <v>0.000354967462780616</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0006560765705127005</v>
+        <v>0.0006588307583789788</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4545738164146216</v>
+        <v>0.4557629785180999</v>
       </c>
     </row>
     <row r="76">
@@ -7946,17 +7782,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.001011053741889413</v>
+        <v>0.001013798221159595</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0003549771713767124</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+        <v>0.000354967462780616</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7965,17 +7795,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.441732096431059</v>
+        <v>1.441358558619673</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9662675791066537</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+        <v>0.9662677857794193</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7984,22 +7808,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>45.74844854021195</v>
+        <v>46.33650066628223</v>
       </c>
       <c r="C79" t="n">
-        <v>18.59260911252091</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+        <v>18.59261326781653</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t># NaN (above ULOQ)</t>
+          <t>Count NaN (above ULOQ)</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -8008,17 +7826,11 @@
       <c r="C80" t="n">
         <v>8</v>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t># =0 (below LLOQ)</t>
+          <t>Count = 0 (below LLOQ)</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -8027,12 +7839,6 @@
       <c r="C81" t="n">
         <v>0</v>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8087,9 +7893,6 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8100,9 +7903,6 @@
       </c>
       <c r="C4" t="n">
         <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -8369,25 +8169,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009330167781206166</v>
+        <v>0.0009330071990155846</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00202179807649072</v>
+        <v>0.002021788741291785</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003584905653194677</v>
+        <v>0.003584908737811873</v>
       </c>
       <c r="E3" t="n">
-        <v>19.20068078583074</v>
+        <v>19.20068507534592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0009304555546071245</v>
+        <v>0.0009304565329349599</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001860911109214249</v>
+        <v>0.001860913065869921</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003575924332929174</v>
+        <v>0.003575927404841796</v>
       </c>
     </row>
     <row r="4">
@@ -8395,25 +8195,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0008846577408462205</v>
+        <v>0.0008846481509079616</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001847595718936192</v>
+        <v>0.001847586344712842</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003318956892865033</v>
+        <v>0.003318959785372463</v>
       </c>
       <c r="E4" t="n">
-        <v>19.44057006746355</v>
+        <v>19.44057441081033</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008737683455005761</v>
+        <v>0.0008737692642246261</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001747536691001153</v>
+        <v>0.001747538528449251</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003311303702941975</v>
+        <v>0.003311306584425004</v>
       </c>
     </row>
     <row r="5">
@@ -8421,25 +8221,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0009009611558619838</v>
+        <v>0.000900951569576011</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001957917164231153</v>
+        <v>0.001957907814721875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003474532674921063</v>
+        <v>0.003474535680361865</v>
       </c>
       <c r="E5" t="n">
-        <v>19.29775573341368</v>
+        <v>19.29776004470752</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009071029975446591</v>
+        <v>0.0009071039513184397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001814205995089318</v>
+        <v>0.001814207902636881</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003466116122974567</v>
+        <v>0.003466119116420138</v>
       </c>
     </row>
     <row r="6">
@@ -8447,25 +8247,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0009351650782737809</v>
+        <v>0.0009351554996500847</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002010607370739102</v>
+        <v>0.002010598033033264</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003534404126894479</v>
+        <v>0.003534407175380116</v>
       </c>
       <c r="E6" t="n">
-        <v>19.24467899786651</v>
+        <v>19.24468329731244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009198005713502102</v>
+        <v>0.0009198015384748615</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001839601142700422</v>
+        <v>0.001839603076949722</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003525683614006488</v>
+        <v>0.003525686650114221</v>
       </c>
     </row>
     <row r="7">
@@ -8473,25 +8273,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0009772420854148444</v>
+        <v>0.0009772325162171001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002054541964755551</v>
+        <v>0.002054532636891736</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003766637169274762</v>
+        <v>0.003766640382599485</v>
       </c>
       <c r="E7" t="n">
-        <v>19.04787950662922</v>
+        <v>19.04788376191822</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009683874394696279</v>
+        <v>0.0009683884576809584</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001936774878939257</v>
+        <v>0.001936776915361918</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003756683778903488</v>
+        <v>0.003756686978319159</v>
       </c>
     </row>
     <row r="8">
@@ -8499,25 +8299,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.000892401614648499</v>
+        <v>0.0008923920264448711</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001907506616367071</v>
+        <v>0.00190749725556478</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003321252790925533</v>
+        <v>0.003321255685111057</v>
       </c>
       <c r="E8" t="n">
-        <v>19.43840885558004</v>
+        <v>19.43841319842378</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008742639082503624</v>
+        <v>0.0008742648274954706</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001748527816500723</v>
+        <v>0.001748529654990941</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003313588613082881</v>
+        <v>0.003313591496229953</v>
       </c>
     </row>
     <row r="9">
@@ -8525,25 +8325,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001104049752386441</v>
+        <v>0.001104040211595769</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002361306158834624</v>
+        <v>0.002361296899691548</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004173443932416452</v>
+        <v>0.004173447426701406</v>
       </c>
       <c r="E9" t="n">
-        <v>18.73376864358822</v>
+        <v>18.73377282849419</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001051076240564707</v>
+        <v>0.001051077345719207</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002102152481129413</v>
+        <v>0.002102154691438415</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004161123011672059</v>
+        <v>0.004161126489192274</v>
       </c>
     </row>
     <row r="10">
@@ -8551,25 +8351,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0008718925849205127</v>
+        <v>0.0008718829921226372</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001851209400877592</v>
+        <v>0.001851200027463697</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003194381600045297</v>
+        <v>0.0031943844009712</v>
       </c>
       <c r="E10" t="n">
-        <v>19.5603897472086</v>
+        <v>19.56039411743308</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0008467125702122229</v>
+        <v>0.0008467134604884667</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001693425140424445</v>
+        <v>0.001693426920976933</v>
       </c>
       <c r="H10" t="n">
-        <v>0.003187312199073714</v>
+        <v>0.00318731498972772</v>
       </c>
     </row>
     <row r="11">
@@ -8577,25 +8377,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0009222599051956918</v>
+        <v>0.0009222503236809854</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001969808095569525</v>
+        <v>0.001969798748723993</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003433867780734629</v>
+        <v>0.003433870756808339</v>
       </c>
       <c r="E11" t="n">
-        <v>19.33438889092703</v>
+        <v>19.3343932104833</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0008984376513446686</v>
+        <v>0.0008984385960072691</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001796875302689337</v>
+        <v>0.001796877192014537</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003425654446146463</v>
+        <v>0.003425657410481971</v>
       </c>
     </row>
     <row r="12">
@@ -8603,25 +8403,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0009308259101279264</v>
+        <v>0.000930816330532107</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002001141047743337</v>
+        <v>0.002001131707916942</v>
       </c>
       <c r="D12" t="n">
-        <v>0.003516419855084127</v>
+        <v>0.003516422890663883</v>
       </c>
       <c r="E12" t="n">
-        <v>19.26051653396556</v>
+        <v>19.26052083693698</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0009159939836455717</v>
+        <v>0.000915994946767785</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001831987967291145</v>
+        <v>0.001831989893535569</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003507791242849972</v>
+        <v>0.003507794266167303</v>
       </c>
     </row>
     <row r="13">
@@ -8629,25 +8429,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0009036010804047453</v>
+        <v>0.0009035914947100529</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001960965819757656</v>
+        <v>0.001960956470931312</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00347535552773802</v>
+        <v>0.003475358533771992</v>
       </c>
       <c r="E13" t="n">
-        <v>19.29701938992458</v>
+        <v>19.29702370109116</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0009072779957130755</v>
+        <v>0.0009072789496708582</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00181455599142615</v>
+        <v>0.001814557899341716</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003466934836708364</v>
+        <v>0.003466937830741856</v>
       </c>
     </row>
     <row r="14">
@@ -8655,25 +8455,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0009607111285430446</v>
+        <v>0.0009607015556420176</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002040157747763619</v>
+        <v>0.002040148416677609</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00354247931182921</v>
+        <v>0.003542482366103117</v>
       </c>
       <c r="E14" t="n">
-        <v>19.23759687067716</v>
+        <v>19.23760116849587</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0009215076895125216</v>
+        <v>0.0009215086584321227</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001843015379025045</v>
+        <v>0.001843017316864245</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003533717367549186</v>
+        <v>0.003533720409393168</v>
       </c>
     </row>
     <row r="15">
@@ -8681,25 +8481,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001090513667322067</v>
+        <v>0.0010905041234992</v>
       </c>
       <c r="C15" t="n">
-        <v>0.002276798573283416</v>
+        <v>0.002276789295209036</v>
       </c>
       <c r="D15" t="n">
-        <v>0.004194376605065906</v>
+        <v>0.004194380113550643</v>
       </c>
       <c r="E15" t="n">
-        <v>18.71854321057133</v>
+        <v>18.71854739206653</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001055251585641912</v>
+        <v>0.00105525269518658</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002110503171283823</v>
+        <v>0.002110505390373161</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004181926654774488</v>
+        <v>0.004181930146341765</v>
       </c>
     </row>
     <row r="16">
@@ -8707,25 +8507,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001058038741575618</v>
+        <v>0.001058029190477602</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00232065879356122</v>
+        <v>0.002320649525312319</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004208492444976922</v>
+        <v>0.004208495963023395</v>
       </c>
       <c r="E16" t="n">
-        <v>18.70832401225228</v>
+        <v>18.70832819142282</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001058062952479374</v>
+        <v>0.001058064064980056</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002116125904958748</v>
+        <v>0.002116128129960112</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004195955084494668</v>
+        <v>0.004195958585520367</v>
       </c>
     </row>
     <row r="17">
@@ -8733,25 +8533,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0009533816303246263</v>
+        <v>0.0009533720557817261</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00206943157560412</v>
+        <v>0.002069422251075888</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003681690788545974</v>
+        <v>0.003681693941962593</v>
       </c>
       <c r="E17" t="n">
-        <v>19.11825606847016</v>
+        <v>19.11826033956792</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0009507360966998311</v>
+        <v>0.0009507370963516518</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001901472193399664</v>
+        <v>0.001901474192703303</v>
       </c>
       <c r="H17" t="n">
-        <v>0.003672198315896289</v>
+        <v>0.003672201455972458</v>
       </c>
     </row>
     <row r="18">
@@ -8759,25 +8559,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0009591975097946921</v>
+        <v>0.0009591879365545044</v>
       </c>
       <c r="C18" t="n">
-        <v>0.002066384699038676</v>
+        <v>0.002066375373827817</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003646749472809597</v>
+        <v>0.003646752601455414</v>
       </c>
       <c r="E18" t="n">
-        <v>19.14773156900712</v>
+        <v>19.1477358466943</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0009434353973430811</v>
+        <v>0.0009434363893185784</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001886870794686163</v>
+        <v>0.001886872778637156</v>
       </c>
       <c r="H18" t="n">
-        <v>0.003637443254204696</v>
+        <v>0.003637446369741092</v>
       </c>
     </row>
     <row r="20">
@@ -8787,25 +8587,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0009340909281971987</v>
+        <v>0.0009340813493328346</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002016202723614911</v>
+        <v>0.002016193387162525</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003538441719361845</v>
+        <v>0.003538444770741616</v>
       </c>
       <c r="E20" t="n">
-        <v>19.24113793427183</v>
+        <v>19.24114223290416</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0009206541304313659</v>
+        <v>0.0009206550984534921</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001841308260862733</v>
+        <v>0.001841310196906983</v>
       </c>
       <c r="H20" t="n">
-        <v>0.003529700490777837</v>
+        <v>0.003529703529753694</v>
       </c>
     </row>
     <row r="21">
@@ -8815,25 +8615,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0008718925849205127</v>
+        <v>0.0008718829921226372</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001847595718936192</v>
+        <v>0.001847586344712842</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003194381600045297</v>
+        <v>0.0031943844009712</v>
       </c>
       <c r="E21" t="n">
-        <v>18.70832401225228</v>
+        <v>18.70832819142282</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0008467125702122229</v>
+        <v>0.0008467134604884667</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001693425140424445</v>
+        <v>0.001693426920976933</v>
       </c>
       <c r="H21" t="n">
-        <v>0.003187312199073714</v>
+        <v>0.00318731498972772</v>
       </c>
     </row>
     <row r="22">
@@ -8843,25 +8643,1267 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001104049752386441</v>
+        <v>0.001104040211595769</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002361306158834624</v>
+        <v>0.002361296899691548</v>
       </c>
       <c r="D22" t="n">
-        <v>0.004208492444976922</v>
+        <v>0.004208495963023395</v>
       </c>
       <c r="E22" t="n">
-        <v>19.5603897472086</v>
+        <v>19.56039411743308</v>
       </c>
       <c r="F22" t="n">
-        <v>0.001058062952479374</v>
+        <v>0.001058064064980056</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002116125904958748</v>
+        <v>0.002116128129960112</v>
       </c>
       <c r="H22" t="n">
-        <v>0.004195955084494668</v>
+        <v>0.004195958585520367</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>R1 Model Fit (nested sampling) vs R2 Model (beta-&gt;inf) — IL-6 dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Method: dynesty nested sampling of the binomial-form quasi-likelihood, nlive=500, bound=multi; logZ and Bayes factors below are descriptive quasi-evidence measures, not exact integer-count Bayesian evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Physical prior: beta &gt;= 1 (each bead has at least 1 binding site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R2 (beta-&gt;inf)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R1 (beta free)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>R1 nominal 95% interval (quasi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8.2265</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7.9956</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[7.9086, 8.0861]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>inf (R2 approx)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[17.57, 31.29]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.003712</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.003510</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[0.003091, 0.003941]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Model Comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Difference / Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>quasi-logL (quasi-MLE)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-124824.28</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-124799.23</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>n_params</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AICc (descriptive, quasi)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>249653.48</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>249606.45</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Δ = -47.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quasi-logZ (nested)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-124838.80</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-124817.44</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>quasi-logBF = 21.36 ± 0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Descriptive quasi-Bayes factor</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>R1 strongly preferred; not exact count-data evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R2_AEB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.997695</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.998415</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nested Sampling Diagnostics</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quasi-logZ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-124817.44 ± 0.33</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-124838.80 ± 0.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>niter</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>9498</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7689</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ncall</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[1 1 1 ... 1 1 1]</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[1 1 1 ... 1 1 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ESS (Kish)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bimodality Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fraction</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>kappa (median [95% CI])</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>beta (median [95% CI])</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A (beta &lt; ~30)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>97.7%</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7.9944 [7.9081, 8.0782]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22.41 [17.57, 29.36]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B (beta &gt;= ~30)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>8.0760 [8.0200, 8.1383]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>33.51 [31.67, 43.86]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Physical interpretation:</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>single intermediate-valency mode (beta ~ 22, &gt;95% of posterior mass); posterior is NOT bimodal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Identifiability:</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>beta bounded away from 1 and infinity -&gt; identifiable at this kappa; R2 approximation error &lt;1% at beta = 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Note:</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>identifiable beta in a calibration experiment does NOT yield calibration-free M0 for unknown samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Derived Quantities (R1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Omega = N*beta</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.12e+07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>kappa*Omega = K*V*N_A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>8.981e+07</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Note: This is a calibration experiment (M known at each</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dilution point). beta identifiability here does NOT imply</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>calibration-free absolute quantification. See SI S2c.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R1 Per-point Predictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Conc (pg/mL)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>P_obs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>P_R2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>P_R1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AEB_R2</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>AEB_R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>85.6</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>29568</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0.002896</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.003712</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0.003486</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.0037</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.0035</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>123.8</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>33529</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0.003693</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.003712</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0.003486</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.0037</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.0035</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0.0328</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>783.3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>31110</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.025178</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0.024011</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0.024313</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.0243</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.0246</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0.0328</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>800.1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>30257</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.026444</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.024011</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.024313</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.0243</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.0246</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0.0984</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1730.7</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>27297</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.063401</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.063376</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.064627</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.0655</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.0668</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0.0984</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2223.6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>33491</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.066393</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.063376</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.064627</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0655</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0668</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0.2960</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3830.5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>23171</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.165314</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.172613</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.175957</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.1895</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.1935</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0.2960</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>6384.6</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>35706</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.178809</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.172613</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.175957</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.1895</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.1935</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0.8880</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>13280.3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>31713</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.418765</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.429368</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.434358</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.5610</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.5698</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0.8880</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>13471.4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>30509</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.441555</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.429368</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0.434358</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.5610</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.5698</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2.6640</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>25090.3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>31098</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.806814</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0.812803</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0.811536</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.6756</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1.6688</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2.6640</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>24884.5</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>30145</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0.825495</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0.812803</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0.811536</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.6756</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1.6688</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>8.0000</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>22722.5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>22988</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0.988450</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0.993424</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0.991120</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>5.0244</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>4.7239</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>8.0000</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>22692.0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>22866</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0.992392</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0.993424</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0.991120</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>5.0244</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>4.7239</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>24.0000</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>28320.0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>28320</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0.999998</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.000000</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0.999995</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>15.0657</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>12.1499</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>24.0000</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>28759.9</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>28760</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0.999996</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.000000</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0.999995</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>15.0657</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>12.1499</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9184,56 +10226,20 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
-      <c r="C22" t="n">
-        <v/>
-      </c>
-      <c r="D22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
-      <c r="C23" t="n">
-        <v/>
-      </c>
-      <c r="D23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
-        <v/>
-      </c>
-      <c r="C24" t="n">
-        <v/>
-      </c>
-      <c r="D24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v/>
-      </c>
-      <c r="C25" t="n">
-        <v/>
-      </c>
-      <c r="D25" t="n">
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -9973,13 +10979,13 @@
         <v>-0.0004000000000000002</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003711984493444581</v>
+        <v>0.00371199061347928</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003718891004422814</v>
+        <v>0.003718897147259649</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0008188910044228145</v>
+        <v>-0.0008188971472596496</v>
       </c>
     </row>
     <row r="3">
@@ -9996,13 +11002,13 @@
         <v>0.0004000000000000002</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003711984493444581</v>
+        <v>0.00371199061347928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003718891004422814</v>
+        <v>0.003718897147259649</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.889100442281416e-05</v>
+        <v>-1.889714725964928e-05</v>
       </c>
     </row>
     <row r="4">
@@ -10013,19 +11019,19 @@
         <v>0.0255</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02429211883001206</v>
+        <v>0.02426963046330552</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001207881169987938</v>
+        <v>0.001230369536694483</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0199842356992416</v>
+        <v>0.01998423810398191</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02430355403103928</v>
+        <v>0.0243035555625517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001196445968960718</v>
+        <v>0.001196444437448294</v>
       </c>
     </row>
     <row r="5">
@@ -10036,19 +11042,19 @@
         <v>0.0268</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02429211883001206</v>
+        <v>0.02426963046330552</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00250788116998794</v>
+        <v>0.002530369536694485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0199842356992416</v>
+        <v>0.01998423810398191</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02430355403103928</v>
+        <v>0.0243035555625517</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002496445968960721</v>
+        <v>0.002496444437448297</v>
       </c>
     </row>
     <row r="6">
@@ -10059,19 +11065,19 @@
         <v>0.0655</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06639900729650675</v>
+        <v>0.06636306782108858</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000899007296506743</v>
+        <v>-0.0008630678210885812</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05173576083375996</v>
+        <v>0.05173575616418257</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06547288008427217</v>
+        <v>0.06547287239313566</v>
       </c>
       <c r="G6" t="n">
-        <v>2.71199157278329e-05</v>
+        <v>2.712760686433835e-05</v>
       </c>
     </row>
     <row r="7">
@@ -10082,19 +11088,19 @@
         <v>0.0687</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06639900729650675</v>
+        <v>0.06636306782108858</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002300992703493251</v>
+        <v>0.002336932178911413</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05173576083375996</v>
+        <v>0.05173575616418257</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06547288008427217</v>
+        <v>0.06547287239313566</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003227119915727827</v>
+        <v>0.003227127606864333</v>
       </c>
     </row>
     <row r="8">
@@ -10105,19 +11111,19 @@
         <v>0.1807</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1931622621108194</v>
+        <v>0.1931413792284241</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01246226211081944</v>
+        <v>-0.01244137922842414</v>
       </c>
       <c r="E8" t="n">
-        <v>0.141295238885029</v>
+        <v>0.141295215572331</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1894829231958398</v>
+        <v>0.189482887724285</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.008782923195839787</v>
+        <v>-0.00878288772428501</v>
       </c>
     </row>
     <row r="9">
@@ -10128,19 +11134,19 @@
         <v>0.197</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1931622621108194</v>
+        <v>0.1931413792284241</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00383773788918057</v>
+        <v>0.003858620771575866</v>
       </c>
       <c r="E9" t="n">
-        <v>0.141295238885029</v>
+        <v>0.141295215572331</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1894829231958398</v>
+        <v>0.189482887724285</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007517076804160222</v>
+        <v>0.007517112275714999</v>
       </c>
     </row>
     <row r="10">
@@ -10151,19 +11157,19 @@
         <v>0.5426</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5702025004718201</v>
+        <v>0.5703253581618671</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.02760250047182011</v>
+        <v>-0.02772535816186716</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3620864894727568</v>
+        <v>0.3620864296800343</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5610109875786735</v>
+        <v>0.5610108688783357</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.01841098757867354</v>
+        <v>-0.01841086887833576</v>
       </c>
     </row>
     <row r="11">
@@ -10174,19 +11180,19 @@
         <v>0.5826</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5702025004718201</v>
+        <v>0.5703253581618671</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01239749952817992</v>
+        <v>0.01227464183813287</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3620864894727568</v>
+        <v>0.3620864296800343</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5610109875786735</v>
+        <v>0.5610108688783357</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02158901242132649</v>
+        <v>0.02158913112166427</v>
       </c>
     </row>
     <row r="12">
@@ -10197,19 +11203,19 @@
         <v>1.6441</v>
       </c>
       <c r="C12" t="n">
-        <v>1.671237717173206</v>
+        <v>1.671495483249137</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.02713771717320657</v>
+        <v>-0.02739548324913699</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7384735681546327</v>
+        <v>0.7384734914016396</v>
       </c>
       <c r="F12" t="n">
-        <v>1.675595180727175</v>
+        <v>1.675594812340488</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0314951807271755</v>
+        <v>-0.03149481234048768</v>
       </c>
     </row>
     <row r="13">
@@ -10220,19 +11226,19 @@
         <v>1.7458</v>
       </c>
       <c r="C13" t="n">
-        <v>1.671237717173206</v>
+        <v>1.671495483249137</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07456228282679356</v>
+        <v>0.07430451675086314</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7384735681546327</v>
+        <v>0.7384734914016396</v>
       </c>
       <c r="F13" t="n">
-        <v>1.675595180727175</v>
+        <v>1.675594812340488</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07020481927282463</v>
+        <v>0.07020518765951245</v>
       </c>
     </row>
     <row r="14">
@@ -10243,19 +11249,19 @@
         <v>4.4611</v>
       </c>
       <c r="C14" t="n">
-        <v>4.713986705458439</v>
+        <v>4.709415060732101</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2528867054584394</v>
+        <v>-0.248315060732101</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9820513164389394</v>
+        <v>0.9820513003994896</v>
       </c>
       <c r="F14" t="n">
-        <v>5.024368409691374</v>
+        <v>5.024367291120926</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.563268409691374</v>
+        <v>-0.5632672911209262</v>
       </c>
     </row>
     <row r="15">
@@ -10266,19 +11272,19 @@
         <v>4.8785</v>
       </c>
       <c r="C15" t="n">
-        <v>4.713986705458439</v>
+        <v>4.709415060732101</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1645132945415604</v>
+        <v>0.1690849392678988</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9820513164389394</v>
+        <v>0.9820513003994896</v>
       </c>
       <c r="F15" t="n">
-        <v>5.024368409691374</v>
+        <v>5.024367291120926</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1458684096913743</v>
+        <v>-0.1458672911209264</v>
       </c>
     </row>
     <row r="16">
@@ -10289,19 +11295,19 @@
         <v>13.2759</v>
       </c>
       <c r="C16" t="n">
-        <v>11.94387218015903</v>
+        <v>11.89097917186772</v>
       </c>
       <c r="D16" t="n">
-        <v>1.332027819840967</v>
+        <v>1.384920828132278</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999941745699672</v>
+        <v>0.9999941745542783</v>
       </c>
       <c r="F16" t="n">
-        <v>15.06566744729551</v>
+        <v>15.06566407895889</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.789767447295512</v>
+        <v>-1.789764078958893</v>
       </c>
     </row>
     <row r="17">
@@ -10312,19 +11318,19 @@
         <v>12.3785</v>
       </c>
       <c r="C17" t="n">
-        <v>11.94387218015903</v>
+        <v>11.89097917186772</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4346278198409674</v>
+        <v>0.4875208281322791</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999941745699672</v>
+        <v>0.9999941745542783</v>
       </c>
       <c r="F17" t="n">
-        <v>15.06566744729551</v>
+        <v>15.06566407895889</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.687167447295511</v>
+        <v>-2.687164078958892</v>
       </c>
     </row>
   </sheetData>
@@ -10380,9 +11386,8 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.00252852916278</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>1.003004735156726</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10391,7 +11396,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>359.245646844495</v>
+        <v>349.3847932490023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -10406,9 +11411,8 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.64253879384457</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>49.37849607926199</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10417,7 +11421,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.226510783248591</v>
+        <v>8.226512850148808</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -10432,7 +11436,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003711984493444581</v>
+        <v>0.00371199061347928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -10496,7 +11500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10548,19 +11552,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.00252852916278</v>
+        <v>1.003004735156726</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9858122412817122</v>
+        <v>0.9862932436545339</v>
       </c>
       <c r="E2" t="n">
-        <v>1.020882908304793</v>
+        <v>1.021444826915104</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03507066702308104</v>
+        <v>0.03515158326057055</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03498221347612804</v>
+        <v>0.03504627847552275</v>
       </c>
     </row>
     <row r="3">
@@ -10575,19 +11579,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>359.245646844495</v>
+        <v>349.3847932490023</v>
       </c>
       <c r="D3" t="n">
-        <v>358.6587816431498</v>
+        <v>348.810866834527</v>
       </c>
       <c r="E3" t="n">
-        <v>359.7665568284839</v>
+        <v>349.8923250018368</v>
       </c>
       <c r="F3" t="n">
-        <v>1.107775185334106</v>
+        <v>1.081458167309847</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00308361477742171</v>
+        <v>0.0030953212280739</v>
       </c>
     </row>
     <row r="4">
@@ -10602,19 +11606,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.64253879384457</v>
+        <v>49.37849607926199</v>
       </c>
       <c r="D4" t="n">
-        <v>46.73476049468378</v>
+        <v>45.57823453215656</v>
       </c>
       <c r="E4" t="n">
-        <v>55.05477870163286</v>
+        <v>53.65898585206882</v>
       </c>
       <c r="F4" t="n">
-        <v>8.320018206949086</v>
+        <v>8.080751319912252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1642891214600868</v>
+        <v>0.1636491987714873</v>
       </c>
     </row>
     <row r="5">
@@ -10629,19 +11633,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.226510783248591</v>
+        <v>8.226512850148808</v>
       </c>
       <c r="D5" t="n">
-        <v>7.976311038104347</v>
+        <v>7.976312927875107</v>
       </c>
       <c r="E5" t="n">
-        <v>8.5836360977951</v>
+        <v>8.583629057939714</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6073250596907531</v>
+        <v>0.6073161300646071</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07382535265466762</v>
+        <v>0.07382424863696911</v>
       </c>
     </row>
     <row r="6">
@@ -10656,35 +11660,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.003711984493444581</v>
+        <v>0.00371199061347928</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003083916053059324</v>
+        <v>0.003083931648023783</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006835562087233455</v>
+        <v>0.006835538539892807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003751646034174131</v>
+        <v>0.003751606891869024</v>
       </c>
       <c r="G6" t="n">
-        <v>1.01068472694312</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+        <v>1.010672515777892</v>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
-      <c r="A8">
-        <f>= Correlations ρ (KEY CLAIM) ==</f>
-        <v/>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correlations ρ (bootstrap)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10698,12 +11695,8 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.06730164501214772</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+        <v>-0.0607753141159412</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10717,12 +11710,8 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3672939046638418</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>0.7717166717075514</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10736,12 +11725,8 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8892220011398669</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+        <v>0.5099156084851008</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10755,12 +11740,42 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3529232807751658</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+        <v>0.352924959610284</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Case resampling</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4PL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14 nonblank wells</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Case resampling</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>All 16 wells, including the blank</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10801,54 +11816,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logL</t>
+          <t>quasi-logL (binomial-form)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-124799.5032245236</v>
+        <v>-124799.510574716</v>
       </c>
       <c r="C2" t="n">
-        <v>-124824.2760542102</v>
+        <v>-124824.2760542014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Higher = better fit</t>
+          <t>Higher = better; AEB-derived effective counts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AICc</t>
+          <t>AICc (descriptive, quasi)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>249607.0064490471</v>
+        <v>249607.0211494321</v>
       </c>
       <c r="C3" t="n">
-        <v>249653.4751853435</v>
+        <v>249653.4751853259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lower = better (penalizes complexity)</t>
+          <t>Lower within the same quasi-likelihood</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>BIC (descriptive, quasi)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>249607.3242152139</v>
+        <v>249607.3389155988</v>
       </c>
       <c r="C4" t="n">
-        <v>249654.0972858649</v>
+        <v>249654.0972858473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lower = better</t>
+          <t>Lower within the same quasi-likelihood</t>
         </is>
       </c>
     </row>
@@ -10859,10 +11874,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9984165206947394</v>
+        <v>0.998417465446286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9976950820740458</v>
+        <v>0.9976950833010773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -10873,18 +11888,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shapiro-Wilk p (residuals)</t>
+          <t>Shapiro-Wilk p (quasi-deviance residuals)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6202703979835803</v>
+        <v>0.633988672980774</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8882526512655635</v>
+        <v>0.8882546425062585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Higher = more normal</t>
+          <t>Descriptive residual diagnostic</t>
         </is>
       </c>
     </row>
@@ -10952,45 +11967,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOO total logL (4PL)</t>
+          <t>LOO total predictive quasi-score (4PL)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-124867.0285035436</v>
+        <v>-124865.3817153827</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sum across wells</t>
+          <t>Sum of held-out quasi-log-likelihoods</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOO total logL (TCS)</t>
+          <t>LOO total predictive quasi-score (TCS)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-124854.6951896058</v>
+        <v>-124854.6934286083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sum across wells</t>
+          <t>Sum of held-out quasi-log-likelihoods</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mean diff (4PL - TCS)</t>
+          <t>Mean Δ predictive quasi-score (4PL - TCS)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7708321211118327</v>
+        <v>-0.6680179233984549</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Positive = TCS better</t>
+          <t>Positive = 4PL higher; negative = TCS higher</t>
         </is>
       </c>
     </row>
@@ -11001,9 +12016,8 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.981253693487567</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>1.991662807523578</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11012,26 +12026,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3890628058615503</v>
+        <v>-0.3354071386356129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paired t-test LOO</t>
+          <t>Paired t-test on predictive quasi-scores</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TOST margin (±logL)</t>
+          <t>TOST margin (±quasi-logL)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78.03418449350363</v>
+        <v>78.03418339288021</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1% of mean per-fold |logL|</t>
+          <t>1% of mean per-fold |quasi-logL|</t>
         </is>
       </c>
     </row>
@@ -11043,10 +12057,9 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[-4.244, 2.702]</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>[-4.160, 2.823]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11066,15 +12079,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Smallest passing margin (logL)</t>
+          <t>Smallest passing margin (quasi-logL)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.244069613197434</v>
+        <v>4.159503116547295</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.054% of per-fold |logL|</t>
+          <t>0.053% of per-fold |quasi-logL|</t>
         </is>
       </c>
     </row>
@@ -11303,7 +12316,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3432</v>
+        <v>0.3434</v>
       </c>
       <c r="F5" t="n">
         <v>0.4349</v>
@@ -11332,7 +12345,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2323</v>
+        <v>2.2321</v>
       </c>
       <c r="F6" t="n">
         <v>2.8437</v>
@@ -11361,7 +12374,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6307</v>
       </c>
       <c r="F7" t="n">
         <v>0.8023</v>
@@ -11390,7 +12403,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7642</v>
+        <v>0.7644</v>
       </c>
       <c r="F8" t="n">
         <v>0.9732</v>
@@ -11419,7 +12432,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0989</v>
+        <v>2.0987</v>
       </c>
       <c r="F9" t="n">
         <v>2.6743</v>
@@ -11448,7 +12461,7 @@
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5606</v>
+        <v>0.5608</v>
       </c>
       <c r="F10" t="n">
         <v>0.7129</v>
@@ -11477,7 +12490,7 @@
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>15.084</v>
+        <v>15.0845</v>
       </c>
       <c r="F11" t="n">
         <v>18.5688</v>
@@ -11506,7 +12519,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1251</v>
+        <v>2.1249</v>
       </c>
       <c r="F12" t="n">
         <v>2.7076</v>
@@ -11525,12 +12538,6 @@
       <c r="A13" t="n">
         <v>9</v>
       </c>
-      <c r="B13" t="n">
-        <v/>
-      </c>
-      <c r="C13" t="n">
-        <v/>
-      </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
@@ -11562,12 +12569,6 @@
       <c r="A14" t="n">
         <v>10</v>
       </c>
-      <c r="B14" t="n">
-        <v/>
-      </c>
-      <c r="C14" t="n">
-        <v/>
-      </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
@@ -11609,7 +12610,7 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>150.7742</v>
+        <v>152.316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -11640,7 +12641,7 @@
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6013</v>
+        <v>2.6009</v>
       </c>
       <c r="F16" t="n">
         <v>3.3117</v>
@@ -11669,7 +12670,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>179.7675</v>
+        <v>182.0306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -11700,7 +12701,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>23.2598</v>
+        <v>23.2715</v>
       </c>
       <c r="F18" t="n">
         <v>27.9666</v>
@@ -11729,7 +12730,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>42.5431</v>
+        <v>42.6198</v>
       </c>
       <c r="F19" t="n">
         <v>48.4393</v>
@@ -11758,7 +12759,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>76.36660000000001</v>
+        <v>76.697</v>
       </c>
       <c r="F20" t="n">
         <v>79.4699</v>
@@ -11787,10 +12788,10 @@
         <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>49.1091</v>
+        <v>49.221</v>
       </c>
       <c r="F21" t="n">
-        <v>54.9156</v>
+        <v>54.9157</v>
       </c>
       <c r="G21" t="n">
         <v>7.959</v>
@@ -11816,7 +12817,7 @@
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7829</v>
+        <v>13.7825</v>
       </c>
       <c r="F22" t="n">
         <v>17.0308</v>
@@ -11845,10 +12846,10 @@
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>92.12779999999999</v>
+        <v>92.639</v>
       </c>
       <c r="F23" t="n">
-        <v>92.1604</v>
+        <v>92.1605</v>
       </c>
       <c r="G23" t="n">
         <v>7.967</v>
@@ -11874,7 +12875,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>27.2458</v>
+        <v>27.2664</v>
       </c>
       <c r="F24" t="n">
         <v>32.387</v>
@@ -11903,7 +12904,7 @@
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>66.2846</v>
+        <v>66.52030000000001</v>
       </c>
       <c r="F25" t="n">
         <v>70.7987</v>
@@ -11932,7 +12933,7 @@
         <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>56.4626</v>
+        <v>56.6219</v>
       </c>
       <c r="F26" t="n">
         <v>61.8963</v>
@@ -11961,7 +12962,7 @@
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>4.6065</v>
+        <v>4.6053</v>
       </c>
       <c r="F27" t="n">
         <v>5.8385</v>
@@ -11990,7 +12991,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>7.0968</v>
+        <v>7.095</v>
       </c>
       <c r="F28" t="n">
         <v>8.936299999999999</v>
@@ -12019,7 +13020,7 @@
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>2.2953</v>
+        <v>2.2951</v>
       </c>
       <c r="F29" t="n">
         <v>2.9237</v>
@@ -12048,7 +13049,7 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>1.883</v>
+        <v>1.8829</v>
       </c>
       <c r="F30" t="n">
         <v>2.3998</v>
@@ -12077,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>19.2335</v>
+        <v>19.3176</v>
       </c>
       <c r="F31" t="n">
         <v>19.9862</v>
@@ -12106,7 +13107,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.2025</v>
+        <v>6.2062</v>
       </c>
       <c r="F32" t="n">
         <v>7.4245</v>
@@ -12135,7 +13136,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>2.0392</v>
+        <v>2.0387</v>
       </c>
       <c r="F33" t="n">
         <v>2.5602</v>
@@ -12164,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7623</v>
+        <v>0.7621</v>
       </c>
       <c r="F34" t="n">
         <v>0.9696</v>
@@ -12251,7 +13252,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0288</v>
+        <v>0.0289</v>
       </c>
       <c r="F37" t="n">
         <v>0.0359</v>
@@ -12359,27 +13360,27 @@
         <v>30</v>
       </c>
       <c r="C42" t="n">
-        <v>1.0459</v>
+        <v>1.0414</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.0222-1.0696</t>
+          <t>1.0171-1.0657</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9963</v>
+        <v>0.9961</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>18.83</v>
+        <v>18.73</v>
       </c>
       <c r="H42" t="n">
-        <v>4.21</v>
+        <v>3.81</v>
       </c>
       <c r="I42" t="n">
-        <v>33.44</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="43">
@@ -12392,23 +13393,22 @@
         <v>29</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2937</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>0.2966</v>
+      </c>
       <c r="E43" t="n">
-        <v>0.9806</v>
+        <v>0.9801</v>
       </c>
       <c r="F43" t="n">
         <v>0.9788</v>
       </c>
       <c r="G43" t="n">
-        <v>-102.73</v>
+        <v>-102.6</v>
       </c>
       <c r="H43" t="n">
-        <v>-138.55</v>
+        <v>-138.4</v>
       </c>
       <c r="I43" t="n">
-        <v>-66.91</v>
+        <v>-66.81</v>
       </c>
     </row>
     <row r="44">
@@ -12423,7 +13423,6 @@
       <c r="C44" t="n">
         <v>0.2885</v>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
         <v>0.9716</v>
       </c>
@@ -12452,7 +13451,6 @@
       <c r="C45" t="n">
         <v>0.3497</v>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
         <v>0.9829</v>
       </c>
